--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -544,42 +544,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>160573.74</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>160573.74</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099801</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099801</t>
         </is>
       </c>
     </row>
@@ -606,42 +602,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>137884.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>20341.15</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>117543.63</v>
+        <v>137884.78</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099802</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099802</t>
         </is>
       </c>
     </row>
@@ -668,42 +660,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>149318.61</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>110961.65</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>38356.96</v>
+        <v>149318.61</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>74.31</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099803</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099803</t>
         </is>
       </c>
     </row>
@@ -730,42 +718,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>69730.64</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>7065.82</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>62664.82</v>
+        <v>69730.64</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10.13</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099804</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099804</t>
         </is>
       </c>
     </row>
@@ -792,42 +776,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>82009.92</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38872.43</v>
+        <v>120882.35</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>67.84</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>425.11</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099805</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099805</t>
         </is>
       </c>
     </row>
@@ -854,42 +834,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>85383.64</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30073.88</v>
+        <v>115457.52</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>73.95</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>877.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099806</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099806</t>
         </is>
       </c>
     </row>
@@ -916,42 +892,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>103743.08</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57170.18</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46572.9</v>
+        <v>103743.08</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>55.11</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>2254.52</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099807</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099807</t>
         </is>
       </c>
     </row>
@@ -978,42 +950,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>101232.21</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1852.8</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>99379.41</v>
+        <v>101232.21</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>17.06</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099808</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099808</t>
         </is>
       </c>
     </row>
@@ -1040,42 +1008,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>30796.35</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>33727.3</v>
+        <v>64523.65</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>47.73</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>148.52</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099809</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099809</t>
         </is>
       </c>
     </row>
@@ -1102,42 +1066,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>120920.56</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>120920.56</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099500</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099500</t>
         </is>
       </c>
     </row>
@@ -1164,42 +1124,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>105.21</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42407.54</v>
+        <v>42512.75</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099701</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099701</t>
         </is>
       </c>
     </row>
@@ -1226,42 +1182,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2941.63</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35539.51</v>
+        <v>38481.14</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.64</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>67.45999999999999</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099705</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099705</t>
         </is>
       </c>
     </row>
@@ -1288,42 +1240,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
         <v>31834.46</v>
       </c>
       <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>31834.46</v>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>29-07-2026</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099702</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099702</t>
         </is>
       </c>
     </row>
@@ -1350,42 +1298,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
         <v>11830.05</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>227.91</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>11602.14</v>
+        <v>11830.05</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>26423.78</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099810</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099810</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1356,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
@@ -1443,7 +1387,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099811</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099811</t>
         </is>
       </c>
     </row>
@@ -1470,42 +1414,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>208.77</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5263.73</v>
+        <v>5472.5</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>9.029999999999999</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099704</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099704</t>
         </is>
       </c>
     </row>
@@ -1532,42 +1472,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
         <v>2377.67</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>28.39</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2349.28</v>
+        <v>2377.67</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>24-07-2026</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099812</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099812</t>
         </is>
       </c>
     </row>
@@ -1594,42 +1530,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2867.28</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>664.63</v>
+        <v>3531.91</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>81.18000000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>90.63</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099703</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099703</t>
         </is>
       </c>
     </row>
@@ -1656,42 +1588,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
         <v>5564.01</v>
       </c>
       <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>5564.01</v>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099600</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099600</t>
         </is>
       </c>
     </row>
@@ -1718,42 +1646,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
         <v>4271.87</v>
       </c>
       <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>4271.87</v>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099700</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099700</t>
         </is>
       </c>
     </row>
@@ -1882,42 +1806,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>79917.56</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099854</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099854</t>
         </is>
       </c>
     </row>
@@ -1944,42 +1864,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>53152.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>34946.25</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18206.33</v>
+        <v>53152.58</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>65.75</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099855</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099855</t>
         </is>
       </c>
     </row>
@@ -2006,42 +1922,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>52709.57</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46500.51</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6209.06</v>
+        <v>52709.57</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>88.22</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099856</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099856</t>
         </is>
       </c>
     </row>
@@ -2068,42 +1980,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>23294.11</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>16419.03</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6875.08</v>
+        <v>23294.11</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>70.48999999999999</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099857</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099857</t>
         </is>
       </c>
     </row>
@@ -2130,42 +2038,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>20671.86</v>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>231.02</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099858</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099858</t>
         </is>
       </c>
     </row>
@@ -2192,42 +2096,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7238.98</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1045.87</v>
+        <v>8284.85</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>87.38</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>460.69</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099859</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099859</t>
         </is>
       </c>
     </row>
@@ -2254,42 +2154,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>22682.31</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>17476.32</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5205.99</v>
+        <v>22682.31</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>77.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>488.32</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099509</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099509</t>
         </is>
       </c>
     </row>
@@ -2316,42 +2212,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>18829.77</v>
       </c>
       <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>18829.77</v>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099609</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099609</t>
         </is>
       </c>
     </row>
@@ -2378,42 +2270,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>527.72</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6887.25</v>
+        <v>7414.97</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>31.53</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099727</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099727</t>
         </is>
       </c>
     </row>
@@ -2440,42 +2328,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>7007.71</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>7007.71</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099728</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099728</t>
         </is>
       </c>
     </row>
@@ -2502,42 +2386,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
         <v>5260.44</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2195.89</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3064.55</v>
+        <v>5260.44</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41.74</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099491</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099491</t>
         </is>
       </c>
     </row>
@@ -2666,42 +2546,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2941.05</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2054.91</v>
+        <v>4995.96</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>58.87</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>15.51</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099860</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099860</t>
         </is>
       </c>
     </row>
@@ -2728,42 +2604,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>8960.700000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8955.41</v>
+        <v>8960.700000000001</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>03-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099861</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099861</t>
         </is>
       </c>
     </row>
@@ -2790,42 +2662,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4789.08</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1715.7</v>
+        <v>6504.78</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>73.62</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>18.58</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099862</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099862</t>
         </is>
       </c>
     </row>
@@ -2852,42 +2720,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>158.07</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2220.78</v>
+        <v>2378.85</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099863</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099863</t>
         </is>
       </c>
     </row>
@@ -2914,42 +2778,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>5183.78</v>
       </c>
       <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>5183.78</v>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099864</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099864</t>
         </is>
       </c>
     </row>
@@ -2976,42 +2836,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>3431.79</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3430.28</v>
+        <v>3431.79</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099865</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099865</t>
         </is>
       </c>
     </row>
@@ -3038,42 +2894,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>3021.64</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2175.47</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>846.17</v>
+        <v>3021.64</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099866</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099866</t>
         </is>
       </c>
     </row>
@@ -3100,42 +2952,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>2806.15</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>86.2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2719.95</v>
+        <v>2806.15</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099510</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099510</t>
         </is>
       </c>
     </row>
@@ -3162,42 +3010,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>273.94</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>298.38</v>
+        <v>572.3200000000001</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>47.87</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>45.85</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099610</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099610</t>
         </is>
       </c>
     </row>
@@ -3224,42 +3068,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>427.29</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>78.86</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>348.43</v>
+        <v>427.29</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.46</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099729</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099729</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3126,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
@@ -3317,7 +3157,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099492</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099492</t>
         </is>
       </c>
     </row>
@@ -3446,42 +3286,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6852.49</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6393.73</v>
+        <v>13246.22</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.73</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>892.67</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099867</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099867</t>
         </is>
       </c>
     </row>
@@ -3508,42 +3344,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3234.61</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6873.13</v>
+        <v>10107.74</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>16.22</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099868</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099868</t>
         </is>
       </c>
     </row>
@@ -3570,42 +3402,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>15916.34</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>25471.04</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>62.49</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>239.81</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099869</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099869</t>
         </is>
       </c>
     </row>
@@ -3632,42 +3460,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>10694.7</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6564.84</v>
+        <v>17259.54</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>61.96</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>93.34999999999999</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099870</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099870</t>
         </is>
       </c>
     </row>
@@ -3694,42 +3518,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>13151.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5635.91</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7515.73</v>
+        <v>13151.64</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>42.85</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>9.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099871</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099871</t>
         </is>
       </c>
     </row>
@@ -3756,42 +3576,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>10963.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5568.09</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5395.24</v>
+        <v>10963.33</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50.79</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>108.17</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099872</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099872</t>
         </is>
       </c>
     </row>
@@ -3818,42 +3634,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4225.49</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5287.95</v>
+        <v>9513.440000000001</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44.42</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>73.04000000000001</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099873</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099873</t>
         </is>
       </c>
     </row>
@@ -3880,12 +3692,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -3911,7 +3723,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099511</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099511</t>
         </is>
       </c>
     </row>
@@ -3938,42 +3750,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>6651.3</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1791.27</v>
+        <v>8442.57</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>78.78</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>142.79</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099611</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099611</t>
         </is>
       </c>
     </row>
@@ -4000,42 +3808,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1007.71</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4546.54</v>
+        <v>5554.25</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.14</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>53.53</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099730</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099730</t>
         </is>
       </c>
     </row>
@@ -4062,42 +3866,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>312.02</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>97.03</v>
+        <v>409.05</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>76.28</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099731</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099731</t>
         </is>
       </c>
     </row>
@@ -4124,42 +3924,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
         <v>31.27</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.82</v>
+        <v>31.27</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.82</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099493</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099493</t>
         </is>
       </c>
     </row>
@@ -4288,42 +4084,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>928.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>210.48</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>718.01</v>
+        <v>928.49</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22.67</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099874</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099874</t>
         </is>
       </c>
     </row>
@@ -4350,42 +4142,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>1497.03</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1081.12</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>415.91</v>
+        <v>1497.03</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>72.22</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099875</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099875</t>
         </is>
       </c>
     </row>
@@ -4412,42 +4200,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>515.2</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>110.55</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>404.65</v>
+        <v>515.2</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21.46</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>28-07-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099876</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099876</t>
         </is>
       </c>
     </row>
@@ -4474,42 +4258,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>494.45</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>301.49</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>192.96</v>
+        <v>494.45</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>60.97</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>26.24</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099877</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099877</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4316,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -4567,7 +4347,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099512</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099512</t>
         </is>
       </c>
     </row>
@@ -4594,42 +4374,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>132.17</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>139.21</v>
+        <v>271.38</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>48.7</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099612</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099612</t>
         </is>
       </c>
     </row>
@@ -4656,42 +4432,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>271.23</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>33.57</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>237.66</v>
+        <v>271.23</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12.38</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099732</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099732</t>
         </is>
       </c>
     </row>
@@ -4820,42 +4592,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>351.88</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>174.15</v>
+        <v>526.03</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>66.89</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099813</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099813</t>
         </is>
       </c>
     </row>
@@ -4882,42 +4650,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>127.34</v>
       </c>
       <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>127.34</v>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24-07-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099814</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099814</t>
         </is>
       </c>
     </row>
@@ -4944,42 +4708,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>243.93</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>153.88</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>90.05</v>
+        <v>243.93</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>63.08</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099815</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099815</t>
         </is>
       </c>
     </row>
@@ -5006,42 +4766,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>35.59</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.09</v>
+        <v>35.59</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43.55</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099816</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099816</t>
         </is>
       </c>
     </row>
@@ -5068,12 +4824,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -5099,7 +4855,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099501</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099501</t>
         </is>
       </c>
     </row>
@@ -5126,42 +4882,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>44.89</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>40.46</v>
+        <v>44.89</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>07-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099601</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099601</t>
         </is>
       </c>
     </row>
@@ -5188,42 +4940,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>60.94</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>12.02</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>48.92</v>
+        <v>60.94</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19.72</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099706</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099706</t>
         </is>
       </c>
     </row>
@@ -5352,42 +5100,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>33586.54</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>82.75</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33503.79</v>
+        <v>33586.54</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099817</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099817</t>
         </is>
       </c>
     </row>
@@ -5414,42 +5158,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>28445.16</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>39048.42</v>
+        <v>67493.58</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42.14</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>3019.97</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099818</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099818</t>
         </is>
       </c>
     </row>
@@ -5476,42 +5216,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>51553.1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12099.57</v>
+        <v>63652.67</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>80.98999999999999</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>312.87</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099819</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099819</t>
         </is>
       </c>
     </row>
@@ -5538,42 +5274,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>23525.09</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>36627.82</v>
+        <v>60152.91</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>39.11</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>64.86</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099820</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099820</t>
         </is>
       </c>
     </row>
@@ -5600,42 +5332,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>357.36</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19477.27</v>
+        <v>19834.63</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>16.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099821</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099821</t>
         </is>
       </c>
     </row>
@@ -5662,42 +5390,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>29457.81</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>665.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>28792.38</v>
+        <v>29457.81</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>5.89</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099822</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099822</t>
         </is>
       </c>
     </row>
@@ -5724,42 +5448,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>25032.18</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1517.3</v>
+        <v>26549.48</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>94.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>37.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099823</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099823</t>
         </is>
       </c>
     </row>
@@ -5786,12 +5506,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -5817,7 +5537,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099502</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099502</t>
         </is>
       </c>
     </row>
@@ -5844,42 +5564,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>24933.92</v>
       </c>
       <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>24933.92</v>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>27-07-2026</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099602</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099602</t>
         </is>
       </c>
     </row>
@@ -5906,42 +5622,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>21283.6</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>13616.54</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7667.06</v>
+        <v>21283.6</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>63.98</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>55.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099707</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099707</t>
         </is>
       </c>
     </row>
@@ -5968,42 +5680,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
         <v>1294.54</v>
       </c>
       <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>1294.54</v>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099709</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099709</t>
         </is>
       </c>
     </row>
@@ -6030,42 +5738,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>457.95</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>287.7</v>
+        <v>745.65</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>61.42</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099710</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099710</t>
         </is>
       </c>
     </row>
@@ -6092,42 +5796,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
         <v>3533.82</v>
       </c>
       <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>3533.82</v>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>23-07-2026</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099708</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099708</t>
         </is>
       </c>
     </row>
@@ -6256,12 +5956,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -6287,7 +5987,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099824</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099824</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6014,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -6345,7 +6045,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099825</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099825</t>
         </is>
       </c>
     </row>
@@ -6372,12 +6072,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
@@ -6403,7 +6103,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099826</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099826</t>
         </is>
       </c>
     </row>
@@ -6430,12 +6130,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -6461,7 +6161,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099827</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099827</t>
         </is>
       </c>
     </row>
@@ -6488,12 +6188,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -6519,7 +6219,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099503</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099503</t>
         </is>
       </c>
     </row>
@@ -6546,12 +6246,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -6577,7 +6277,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099603</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099603</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6304,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -6629,17 +6329,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>15-07-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099711</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099711</t>
         </is>
       </c>
     </row>
@@ -6768,42 +6464,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>11837.81</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>11837.81</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>20-07-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099828</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099828</t>
         </is>
       </c>
     </row>
@@ -6830,42 +6522,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>5166.66</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1250.17</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3916.49</v>
+        <v>5166.66</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>24.2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>20-07-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099829</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099829</t>
         </is>
       </c>
     </row>
@@ -6892,42 +6580,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>15495.38</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6285.05</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9210.33</v>
+        <v>15495.38</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>40.56</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099830</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099830</t>
         </is>
       </c>
     </row>
@@ -6954,12 +6638,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -6985,7 +6669,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099831</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099831</t>
         </is>
       </c>
     </row>
@@ -7012,12 +6696,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -7043,7 +6727,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099504</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099504</t>
         </is>
       </c>
     </row>
@@ -7070,42 +6754,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>1478.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1476.64</v>
+        <v>1478.75</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>31-07-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099604</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099604</t>
         </is>
       </c>
     </row>
@@ -7132,42 +6812,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>4094.55</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>16.27</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4078.28</v>
+        <v>4094.55</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099712</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099712</t>
         </is>
       </c>
     </row>
@@ -7194,42 +6870,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>554.14</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>78.3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>475.84</v>
+        <v>554.14</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14.13</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099713</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099713</t>
         </is>
       </c>
     </row>
@@ -7358,42 +7030,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>33338.76</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>33338.76</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099605</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099605</t>
         </is>
       </c>
     </row>
@@ -7420,42 +7088,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>21424.19</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4695.74</v>
+        <v>26119.93</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>82.02</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099836</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099836</t>
         </is>
       </c>
     </row>
@@ -7482,42 +7146,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>21010.94</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>96485.98</v>
+        <v>117496.92</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.88</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>55.91</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099832</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099832</t>
         </is>
       </c>
     </row>
@@ -7544,42 +7204,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>30937.09</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2846.3</v>
+        <v>33783.39</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099833</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099833</t>
         </is>
       </c>
     </row>
@@ -7606,42 +7262,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>63925.33</v>
       </c>
       <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>63925.33</v>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>30-07-2026</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099834</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099834</t>
         </is>
       </c>
     </row>
@@ -7668,42 +7320,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>24757.28</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33538.57</v>
+        <v>58295.85</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>42.47</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>382.91</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099835</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099835</t>
         </is>
       </c>
     </row>
@@ -7730,42 +7378,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>38881.49</v>
       </c>
       <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>38881.49</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>22-07-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099505</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099505</t>
         </is>
       </c>
     </row>
@@ -7792,42 +7436,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11454.32</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>145.76</v>
+        <v>11600.08</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>44.09</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099718</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099718</t>
         </is>
       </c>
     </row>
@@ -7854,42 +7494,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>2874.21</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2873.59</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.62</v>
+        <v>2874.21</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>99.98</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099716</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099716</t>
         </is>
       </c>
     </row>
@@ -7916,42 +7552,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>2943.83</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099715</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099715</t>
         </is>
       </c>
     </row>
@@ -7978,42 +7610,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
         <v>3150.34</v>
       </c>
       <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>3150.34</v>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099717</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099717</t>
         </is>
       </c>
     </row>
@@ -8040,42 +7668,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
         <v>12761.32</v>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099714</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099714</t>
         </is>
       </c>
     </row>
@@ -8204,42 +7828,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>101845.34</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8853.52</v>
+        <v>110698.86</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>361.54</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099837</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099837</t>
         </is>
       </c>
     </row>
@@ -8266,42 +7886,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>45749.21</v>
       </c>
       <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>45749.21</v>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099838</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099838</t>
         </is>
       </c>
     </row>
@@ -8328,42 +7944,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3039.89</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>31262.44</v>
+        <v>34302.33</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>397.84</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099839</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099839</t>
         </is>
       </c>
     </row>
@@ -8390,42 +8002,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>26019.96</v>
       </c>
       <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>26019.96</v>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>20-07-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099840</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099840</t>
         </is>
       </c>
     </row>
@@ -8452,42 +8060,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3270.88</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22240.03</v>
+        <v>25510.91</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12.82</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099841</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099841</t>
         </is>
       </c>
     </row>
@@ -8514,42 +8118,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>19514.4</v>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099506</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099506</t>
         </is>
       </c>
     </row>
@@ -8576,42 +8176,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>23174.68</v>
       </c>
       <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>23174.68</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099606</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099606</t>
         </is>
       </c>
     </row>
@@ -8638,42 +8234,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>22543.14</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>42.03</v>
+        <v>22585.17</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>99.81</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>46.38</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099719</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099719</t>
         </is>
       </c>
     </row>
@@ -8700,42 +8292,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>1878.7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>253.71</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1624.99</v>
+        <v>1878.7</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>9.130000000000001</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099720</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099720</t>
         </is>
       </c>
     </row>
@@ -8762,42 +8350,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>314.48</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099721</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099721</t>
         </is>
       </c>
     </row>
@@ -8926,42 +8510,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>54334.43</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>54334.43</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>07-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099842</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099842</t>
         </is>
       </c>
     </row>
@@ -8988,42 +8568,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>41828.13</v>
       </c>
       <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>41828.13</v>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>31-07-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099843</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099843</t>
         </is>
       </c>
     </row>
@@ -9050,42 +8626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>12605.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8675.17</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3930.73</v>
+        <v>12605.9</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>68.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>20.86</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099844</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099844</t>
         </is>
       </c>
     </row>
@@ -9112,42 +8684,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>11568.94</v>
       </c>
       <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>11568.94</v>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>20-07-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099845</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099845</t>
         </is>
       </c>
     </row>
@@ -9174,42 +8742,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>5322.29</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5227.06</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>95.23</v>
+        <v>5322.29</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>98.20999999999999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099846</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099846</t>
         </is>
       </c>
     </row>
@@ -9236,42 +8800,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4242.37</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3752.77</v>
+        <v>7995.14</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>53.06</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>119.22</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099847</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099847</t>
         </is>
       </c>
     </row>
@@ -9298,42 +8858,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
         <v>12575.71</v>
       </c>
       <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>12575.71</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099507</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099507</t>
         </is>
       </c>
     </row>
@@ -9360,42 +8916,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>6968.09</v>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099607</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099607</t>
         </is>
       </c>
     </row>
@@ -9422,42 +8974,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>530.03</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1407.64</v>
+        <v>1937.67</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>27.35</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>25.48</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099722</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099722</t>
         </is>
       </c>
     </row>
@@ -9484,42 +9032,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>1831.54</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>1831.54</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>23-07-2026</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099723</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099723</t>
         </is>
       </c>
     </row>
@@ -9648,42 +9192,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9020.549999999999</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29331.65</v>
+        <v>38352.2</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>23.52</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>65.84999999999999</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099848</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099848</t>
         </is>
       </c>
     </row>
@@ -9710,42 +9250,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>6776.01</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8435.049999999999</v>
+        <v>15211.06</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>44.55</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>325.88</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099849</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099849</t>
         </is>
       </c>
     </row>
@@ -9772,42 +9308,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8718.43</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6899.59</v>
+        <v>15618.02</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55.82</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>177.21</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099850</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099850</t>
         </is>
       </c>
     </row>
@@ -9834,42 +9366,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
         <v>14278.53</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2704.43</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11574.1</v>
+        <v>14278.53</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18.94</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>376.93</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099851</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099851</t>
         </is>
       </c>
     </row>
@@ -9896,42 +9424,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
         <v>13880.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>6729.27</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7151.15</v>
+        <v>13880.42</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>48.48</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099852</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099852</t>
         </is>
       </c>
     </row>
@@ -9958,42 +9482,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
         <v>11752.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5892.18</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5860.15</v>
+        <v>11752.33</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50.14</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>477.11</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099853</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099853</t>
         </is>
       </c>
     </row>
@@ -10020,12 +9540,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -10051,7 +9571,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099508</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099508</t>
         </is>
       </c>
     </row>
@@ -10078,42 +9598,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
         <v>6446.51</v>
       </c>
       <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>6446.51</v>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099608</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099608</t>
         </is>
       </c>
     </row>
@@ -10140,42 +9656,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1788.57</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4189.17</v>
+        <v>5977.74</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29.92</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>21.09</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099724</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099724</t>
         </is>
       </c>
     </row>
@@ -10202,42 +9714,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
         <v>2917.88</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>2917.88</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>20-07-2026</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099725</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099725</t>
         </is>
       </c>
     </row>
@@ -10264,12 +9772,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>01-10-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-12-2026</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
@@ -10295,7 +9803,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-07-01&amp;Code=099726</t>
+          <t>https://ec.europa.eu/taxation_customs/dds2/taric/quota_tariff_details.jsp?Lang=en&amp;StartDate=2026-10-01&amp;Code=099726</t>
         </is>
       </c>
     </row>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A Non Alloy and Other Alloy Ho" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B Non Alloy and Other Alloy Ho" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Non Alloy and Other Alloy Col" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A Electrical Sheets (other tha" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B Electrical Sheets (other tha" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4A Metallic Coated Sheets" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4B Metallic Coated Sheets" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Organic Coated Sheets" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Tin Mill Products" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Non Alloy and Other Alloy Qua" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Stainless Hot Rolled Sheets a" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 Stainless Cold Rolled Sheets " sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Stainless Hot Rolled Quarto " sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="1A Non Alloy and Other Alloy Ho" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1B Non Alloy and Other Alloy Ho" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2 Non Alloy and Other Alloy Col" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3A Electrical Sheets (other tha" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3B Electrical Sheets (other tha" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4A Metallic Coated Sheets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4B Metallic Coated Sheets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="5 Organic Coated Sheets" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6 Tin Mill Products" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="7 Non Alloy and Other Alloy Qua" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="8 Stainless Hot Rolled Sheets a" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="9 Stainless Cold Rolled Sheets " sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="10 Stainless Hot Rolled Quarto " sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>271032.05</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>64043.63</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3494.39</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>51317.21</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>425.86</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>474.72</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>14802.1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>12026.14</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1984.71</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>9401.440000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>42591.03</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3951.12</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>418.24</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>17669.29</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>8575.77</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1798.36</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1059.65</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>17.26</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4587.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>36.41</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>316.13</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>806.3200000000001</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1845.39</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>20.84</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>209.97</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>23.53</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>129.38</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>498.69</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>6402.99</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>8059.22</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>50.54</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>42322.06</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>7571.38</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>41310.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>932.75</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>66253.64999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3919.63</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5015.02</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>37589.28</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>58692.55</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5601.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3119.98</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5668.77</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>14895.03</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>90246.87</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>18223.6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6144.97</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>14106.02</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>10176.39</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>18.61</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>20680.64</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>29553.36</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2666.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6587.88</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6344.73</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2670.18</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>219.28</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>65.05</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>9086.200000000001</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>271032.05</v>
+        <v>378822.61</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>64043.63</v>
+        <v>102977.12</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>185.27</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>3494.39</v>
+        <v>3623.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>51317.21</v>
+        <v>55407.72</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4885.32</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>425.86</v>
+        <v>476.06</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>19.64</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>474.72</v>
+        <v>6052.08</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>52.71</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>12026.14</v>
+        <v>12089.8</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>9401.440000000001</v>
+        <v>9404.299999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4488.84</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>42591.03</v>
+        <v>64454.45</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>12208.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>3951.12</v>
+        <v>4393.45</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>418.24</v>
+        <v>796.6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>17669.29</v>
+        <v>27801.03</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>8575.77</v>
+        <v>15474.61</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>1798.36</v>
+        <v>1864.65</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>1059.65</v>
+        <v>1131.95</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0.06</v>
+        <v>36.98</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>17.26</v>
+        <v>18.57</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0.9</v>
+        <v>143.49</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>4587.3</v>
+        <v>4867.89</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>36.41</v>
+        <v>54.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>316.13</v>
+        <v>427.97</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>372.65</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>19.86</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>806.3200000000001</v>
+        <v>828.66</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>1845.39</v>
+        <v>2247.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>1.91</v>
+        <v>69.77</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0.51</v>
+        <v>19.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>1.86</v>
+        <v>16.14</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>23.53</v>
+        <v>70.61</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>129.38</v>
+        <v>139.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>16.41</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>498.69</v>
+        <v>3054.62</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>6402.99</v>
+        <v>7224.84</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>8059.22</v>
+        <v>12958.46</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>102.24</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>50.54</v>
+        <v>545.05</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>42322.06</v>
+        <v>53968.35</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>7571.38</v>
+        <v>8086.14</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>41310.5</v>
+        <v>41793.05</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>711.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>66253.64999999999</v>
+        <v>67581.89999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>3919.63</v>
+        <v>4500.51</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>5015.02</v>
+        <v>8065.13</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>58692.55</v>
+        <v>96084.16</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5694.52</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>1.44</v>
+        <v>188.92</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>651.85</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>5668.77</v>
+        <v>5832.01</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>14895.03</v>
+        <v>16920.55</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>90246.87</v>
+        <v>111256.87</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>139.61</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>18223.6</v>
+        <v>26577.38</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>6144.97</v>
+        <v>13448.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>14106.02</v>
+        <v>15485.46</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>10176.39</v>
+        <v>10330.59</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>19.93</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>18.61</v>
+        <v>193.81</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>20680.64</v>
+        <v>41024.58</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>29553.36</v>
+        <v>36292</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>6587.88</v>
+        <v>16073.39</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>6344.73</v>
+        <v>6881.14</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>47.32</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>2670.18</v>
+        <v>3370.27</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>219.28</v>
+        <v>1723.05</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>291.79</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>22.67</v>
+        <v>139.15</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>65.05</v>
+        <v>245.46</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>17.16</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>9086.200000000001</v>
+        <v>9096.879999999999</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -556,22 +556,26 @@
         <v>160573.74</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>160573.74</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>160573.74</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>378822.61</v>
+        <v>3123.38</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -672,22 +676,26 @@
         <v>149318.61</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>102977.12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>149318.61</v>
+        <v>46341.49</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>102977.12</v>
+        <v>27215.45</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -803,7 +811,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>185.27</v>
+        <v>433.1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -846,22 +854,26 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>3623.8</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>115457.52</v>
+        <v>111833.72</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>3623.8</v>
+        <v>4839.65</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -904,22 +916,26 @@
         <v>103743.08</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>55407.72</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>103743.08</v>
+        <v>48335.36</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>53.41</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>55407.72</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1020,22 +1036,26 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>475.1</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>64523.65</v>
+        <v>64048.55</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>476.06</v>
+        <v>1801.03</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1136,22 +1156,26 @@
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>19.64</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42512.75</v>
+        <v>42493.11</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M12" t="n">
-        <v>19.64</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1194,22 +1218,26 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
+        <v>42.6</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38481.14</v>
+        <v>38438.54</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M13" t="n">
-        <v>23.7</v>
+        <v>91.22</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1252,22 +1280,26 @@
         <v>31834.46</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>31498.23</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31834.46</v>
+        <v>336.23</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>98.94</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M14" t="n">
-        <v>6052.08</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1310,22 +1342,26 @@
         <v>11830.05</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
+        <v>11830.05</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>11830.05</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M15" t="n">
-        <v>14802.1</v>
+        <v>0.02</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1426,10 +1462,10 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5472.5</v>
+        <v>5472.41</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0</v>
@@ -1439,9 +1475,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M17" t="n">
-        <v>1.2</v>
+        <v>6.65</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1542,22 +1582,26 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0</v>
+        <v>52.71</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3531.91</v>
+        <v>3479.2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M19" t="n">
-        <v>52.71</v>
+        <v>96.69</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1600,22 +1644,26 @@
         <v>5564.01</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>5564.01</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5564.01</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M20" t="n">
-        <v>12089.8</v>
+        <v>35.08</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1658,22 +1706,26 @@
         <v>4271.87</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0</v>
+        <v>1984.71</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4271.87</v>
+        <v>2287.16</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0</v>
+        <v>46.46</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M21" t="n">
-        <v>1984.71</v>
+        <v>0</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1818,22 +1870,26 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>9404.299999999999</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>79917.56</v>
+        <v>70513.25999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>11.77</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>9404.299999999999</v>
+        <v>4014.08</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1876,22 +1932,26 @@
         <v>53152.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>4488.84</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>53152.58</v>
+        <v>48663.74</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>4488.84</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1934,22 +1994,26 @@
         <v>52709.57</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>52709.57</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>52709.57</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>64454.45</v>
+        <v>1115.83</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2050,22 +2114,26 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>4370.84</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20671.86</v>
+        <v>16301.02</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>21.14</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>4393.45</v>
+        <v>304.09</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2108,22 +2176,26 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>488.32</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>8284.85</v>
+        <v>7796.53</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>796.6</v>
+        <v>708.3200000000001</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2224,22 +2296,26 @@
         <v>18829.77</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>18829.77</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>18829.77</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M9" t="n">
-        <v>27801.03</v>
+        <v>135.19</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2297,7 +2373,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2340,22 +2416,26 @@
         <v>7007.71</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>7007.71</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7007.71</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>15474.61</v>
+        <v>88.25</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2398,20 +2478,24 @@
         <v>5260.44</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>44.96</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5260.44</v>
+        <v>5215.48</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -2558,22 +2642,26 @@
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>1844.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4995.96</v>
+        <v>3151.19</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>36.93</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>1864.65</v>
+        <v>90.62</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2616,22 +2704,26 @@
         <v>8960.700000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8960.700000000001</v>
+        <v>8955.459999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2674,22 +2766,26 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1142.98</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6504.78</v>
+        <v>5361.8</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>17.57</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>1131.95</v>
+        <v>41.44</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2732,10 +2828,10 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2378.85</v>
+        <v>2378.79</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -2745,9 +2841,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>36.98</v>
+        <v>40.33</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2790,22 +2890,26 @@
         <v>5183.78</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>18.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5183.78</v>
+        <v>5165.2</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>18.57</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2863,7 +2967,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3022,22 +3126,26 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>104.29</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>572.3200000000001</v>
+        <v>468.03</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>143.49</v>
+        <v>39.53</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3298,22 +3406,26 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>4789.57</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>13246.22</v>
+        <v>8456.65</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>36.16</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>4867.89</v>
+        <v>280.52</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3356,22 +3468,26 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>50.46</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10107.74</v>
+        <v>10057.28</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>54.3</v>
+        <v>27.84</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3414,22 +3530,26 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>410.3</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25471.04</v>
+        <v>25060.74</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>427.97</v>
+        <v>420.74</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3487,7 +3607,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>372.65</v>
+        <v>517.59</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3530,22 +3650,26 @@
         <v>13151.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13151.64</v>
+        <v>13146.5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>19.86</v>
+        <v>14.72</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3588,22 +3712,26 @@
         <v>10963.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10963.33</v>
+        <v>10962.75</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>0.58</v>
+        <v>399.75</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3646,22 +3774,26 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>806.3200000000001</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9513.440000000001</v>
+        <v>8707.120000000001</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>8.48</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>828.66</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3762,22 +3894,26 @@
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>2166.96</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>8442.57</v>
+        <v>6275.61</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>25.67</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>2247.9</v>
+        <v>283.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3820,22 +3956,26 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>69.77</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5554.25</v>
+        <v>5484.48</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>69.77</v>
+        <v>14.49</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3878,22 +4018,26 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>409.05</v>
+        <v>408.24</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M12" t="n">
-        <v>19.4</v>
+        <v>49.76</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4096,22 +4240,26 @@
         <v>928.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>20.84</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>928.49</v>
+        <v>907.65</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>20.84</v>
+        <v>13.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4154,22 +4302,26 @@
         <v>1497.03</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>209.97</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1497.03</v>
+        <v>1287.06</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>14.03</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>209.97</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4386,22 +4538,26 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>271.38</v>
+        <v>269.52</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>16.14</v>
+        <v>14.28</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4604,22 +4760,26 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>23.53</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>526.03</v>
+        <v>502.5</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>70.61</v>
+        <v>47.08</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4662,22 +4822,26 @@
         <v>127.34</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>127.34</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>127.34</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>139.3</v>
+        <v>9.93</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4720,22 +4884,26 @@
         <v>243.93</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>16.41</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>243.93</v>
+        <v>227.52</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>16.41</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5170,22 +5338,26 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>498.69</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>67493.58</v>
+        <v>66994.89</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>3054.62</v>
+        <v>2555.93</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5228,22 +5400,26 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>6756.95</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>63652.67</v>
+        <v>56895.72</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>10.62</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>7224.84</v>
+        <v>3087.05</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5286,22 +5462,26 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>18305.08</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>60152.91</v>
+        <v>41847.83</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>30.43</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>12958.46</v>
+        <v>7325.66</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5344,22 +5524,26 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>102.24</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19834.63</v>
+        <v>19732.39</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>102.24</v>
+        <v>0.25</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5402,10 +5586,10 @@
         <v>29457.81</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29457.81</v>
+        <v>29457.79</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -5415,7 +5599,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -5460,22 +5648,26 @@
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>526.6900000000001</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26549.48</v>
+        <v>26022.79</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>545.05</v>
+        <v>186.32</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5576,22 +5768,26 @@
         <v>24933.92</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>24933.92</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24933.92</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>53968.35</v>
+        <v>131.13</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5634,22 +5830,26 @@
         <v>21283.6</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>8086.14</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21283.6</v>
+        <v>13197.46</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>37.99</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>8086.14</v>
+        <v>2323.74</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -6476,22 +6676,26 @@
         <v>11837.81</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>11837.81</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>11837.81</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>41793.05</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -6592,22 +6796,26 @@
         <v>15495.38</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>932.75</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15495.38</v>
+        <v>14562.63</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>932.75</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -6781,7 +6989,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7042,22 +7250,26 @@
         <v>33338.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>33338.76</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33338.76</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>67581.89999999999</v>
+        <v>415.31</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7100,22 +7312,26 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>5040.46</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26119.93</v>
+        <v>21079.47</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>4500.51</v>
+        <v>2146.07</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7158,22 +7374,26 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>8065.13</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>117496.92</v>
+        <v>109431.79</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>8065.13</v>
+        <v>2279.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7216,22 +7436,26 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>33783.39</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33783.39</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>37589.28</v>
+        <v>26.9</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -7274,22 +7498,26 @@
         <v>63925.33</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>63925.33</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>63925.33</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>96084.16</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -7332,22 +7560,26 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>58.36</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>58295.85</v>
+        <v>58237.49</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>5694.52</v>
+        <v>10397.14</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7448,22 +7680,26 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11600.08</v>
+        <v>11598.64</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M9" t="n">
-        <v>188.92</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7506,22 +7742,26 @@
         <v>2874.21</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>2874.21</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2874.21</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>5601.7</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -7564,22 +7804,26 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>645.9</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2943.83</v>
+        <v>2297.93</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>21.94</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>651.85</v>
+        <v>32.66</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -7622,22 +7866,26 @@
         <v>3150.34</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>3119.98</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3150.34</v>
+        <v>30.36</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M12" t="n">
-        <v>3119.98</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -7680,22 +7928,26 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
+        <v>5713.85</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>12761.32</v>
+        <v>7047.47</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0</v>
+        <v>44.77</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M13" t="n">
-        <v>5832.01</v>
+        <v>180</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -7840,22 +8092,26 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>18245.97</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>110698.86</v>
+        <v>92452.89</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>16.48</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>16920.55</v>
+        <v>3078.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7898,22 +8154,26 @@
         <v>45749.21</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>45749.21</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45749.21</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>111256.87</v>
+        <v>55.38</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7956,22 +8216,26 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>138.84</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34302.33</v>
+        <v>34163.49</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>139.61</v>
+        <v>21.15</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8014,22 +8278,26 @@
         <v>26019.96</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>26019.96</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26019.96</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>26577.38</v>
+        <v>287.58</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -8072,22 +8340,26 @@
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>6145.08</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25510.91</v>
+        <v>19365.83</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>24.09</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>13448.8</v>
+        <v>10247.04</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8188,22 +8460,26 @@
         <v>23174.68</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>15714.62</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>23174.68</v>
+        <v>7460.06</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>67.81</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>15485.46</v>
+        <v>642.64</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8246,22 +8522,26 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>10330.59</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22585.17</v>
+        <v>12254.58</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>45.74</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M9" t="n">
-        <v>10330.59</v>
+        <v>150</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8304,22 +8584,26 @@
         <v>1878.7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>19.93</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1878.7</v>
+        <v>1858.77</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>19.93</v>
+        <v>7.57</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8362,22 +8646,26 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>132.31</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>314.48</v>
+        <v>182.16</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>42.07</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>193.81</v>
+        <v>98.72</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8522,22 +8810,26 @@
         <v>54334.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>48005.59</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>54334.43</v>
+        <v>6328.84</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>41024.58</v>
+        <v>4736.94</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8580,22 +8872,26 @@
         <v>41828.13</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>39180.29</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>41828.13</v>
+        <v>2647.84</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>93.67</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>36292</v>
+        <v>1342.72</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -8638,22 +8934,26 @@
         <v>12605.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>2666.1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12605.9</v>
+        <v>9939.799999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>21.15</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>2666.1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8696,22 +8996,26 @@
         <v>11568.94</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>11568.94</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11568.94</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>16073.39</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -8754,22 +9058,26 @@
         <v>5322.29</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>5322.29</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5322.29</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>6881.14</v>
+        <v>22.02</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8812,22 +9120,26 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>21.16</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7995.14</v>
+        <v>7973.98</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>47.32</v>
+        <v>184.01</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8928,22 +9240,26 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>3406.36</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6968.09</v>
+        <v>3561.73</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>48.89</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M9" t="n">
-        <v>3370.27</v>
+        <v>249.38</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8986,22 +9302,26 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1937.67</v>
+        <v>1934.93</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>23.53</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9044,22 +9364,26 @@
         <v>1831.54</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>1723.05</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1831.54</v>
+        <v>108.5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>94.08</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>1723.05</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9204,22 +9528,26 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>107.78</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>38352.2</v>
+        <v>38244.43</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>291.79</v>
+        <v>260.92</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9262,22 +9590,26 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>132.55</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15211.06</v>
+        <v>15078.51</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>139.15</v>
+        <v>102.26</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9320,22 +9652,26 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>130.3</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15618.02</v>
+        <v>15487.72</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>245.46</v>
+        <v>275.54</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9393,7 +9729,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -9451,7 +9787,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>17.16</v>
+        <v>775.71</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -9610,22 +9946,26 @@
         <v>6446.51</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>6446.51</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6446.51</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M9" t="n">
-        <v>9096.879999999999</v>
+        <v>843.41</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9683,7 +10023,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9726,22 +10066,26 @@
         <v>2917.88</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>18.72</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2917.88</v>
+        <v>2899.16</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3123.38</v>
+        <v>3355.95</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>27215.45</v>
+        <v>50843.59</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>433.1</v>
+        <v>481.4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4839.65</v>
+        <v>4859.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1801.03</v>
+        <v>2087.04</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>92752.45</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>19.85</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>91.22</v>
+        <v>91.56</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>6.65</v>
+        <v>7.78</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>96.69</v>
+        <v>139.4</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>35.08</v>
+        <v>35.12</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2623.64</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>304.09</v>
+        <v>944.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>708.3200000000001</v>
+        <v>1070.02</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2691.31</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>135.19</v>
+        <v>310.27</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>10.7</v>
+        <v>20.85</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>194.69</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>90.62</v>
+        <v>135.59</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>40.33</v>
+        <v>40.9</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>39.53</v>
+        <v>216.52</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>280.52</v>
+        <v>690.38</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>27.84</v>
+        <v>49.98</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>420.74</v>
+        <v>576.41</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>517.59</v>
+        <v>1080.82</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>14.72</v>
+        <v>40.42</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66.09999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>283.3</v>
+        <v>543.39</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>14.49</v>
+        <v>22.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>49.76</v>
+        <v>49.85</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>14.28</v>
+        <v>24.51</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>27.56</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2555.93</v>
+        <v>3088.61</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3087.05</v>
+        <v>3549.86</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>7325.66</v>
+        <v>7707.53</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>131.13</v>
+        <v>152.84</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>2323.74</v>
+        <v>4265.86</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>21.36</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0.05</v>
+        <v>2.18</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>415.31</v>
+        <v>419.11</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2279.2</v>
+        <v>2418.05</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>27.95</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>10397.14</v>
+        <v>14828.94</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>14098.39</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>514.6799999999999</v>
+        <v>592.72</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>1493.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3078.2</v>
+        <v>3353.77</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>55.38</v>
+        <v>74.22</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>21.15</v>
+        <v>130.96</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>287.58</v>
+        <v>993.03</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>10247.04</v>
+        <v>10248.05</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>381.56</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>642.64</v>
+        <v>885.92</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>150</v>
+        <v>173.51</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4736.94</v>
+        <v>8464.27</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1342.72</v>
+        <v>2258.45</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>184.01</v>
+        <v>968.61</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>423.75</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>249.38</v>
+        <v>1616.88</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>23.53</v>
+        <v>31.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>260.92</v>
+        <v>285.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>102.26</v>
+        <v>282.95</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>275.54</v>
+        <v>418.87</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0.14</v>
+        <v>1023</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>775.71</v>
+        <v>848.36</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>132.81</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,11 +571,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3355.95</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -676,13 +676,13 @@
         <v>149318.61</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>102977.12</v>
+        <v>130192.57</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46341.49</v>
+        <v>19126.04</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>68.95999999999999</v>
+        <v>87.19</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -691,11 +691,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>50843.59</v>
+        <v>23628.14</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>9657.690000000001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -796,22 +796,26 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>481.4</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>120882.35</v>
+        <v>120400.95</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>481.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -854,13 +858,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3623.8</v>
+        <v>8463.450000000001</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>111833.72</v>
+        <v>106994.07</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.14</v>
+        <v>7.33</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +873,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4859.8</v>
+        <v>2295.44</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,22 +982,26 @@
         <v>101232.21</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>4885.32</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>101232.21</v>
+        <v>96346.89</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M9" t="n">
-        <v>4885.32</v>
+        <v>19973.65</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1036,13 +1044,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>475.1</v>
+        <v>2445.44</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>64048.55</v>
+        <v>62078.21</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.74</v>
+        <v>3.79</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1051,11 +1059,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2087.04</v>
+        <v>198.52</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1113,7 +1121,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>92752.45</v>
+        <v>194001.02</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1156,13 +1164,13 @@
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19.64</v>
+        <v>39.49</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42493.11</v>
+        <v>42473.26</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1171,11 +1179,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>19.85</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1218,13 +1226,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>42.6</v>
+        <v>133.82</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38438.54</v>
+        <v>38347.32</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1233,11 +1241,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>91.56</v>
+        <v>16.42</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1357,11 +1365,11 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1462,13 +1470,13 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.09</v>
+        <v>7.85</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5472.41</v>
+        <v>5464.65</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1477,11 +1485,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>7.78</v>
+        <v>10.47</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1582,13 +1590,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.71</v>
+        <v>192.12</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3479.2</v>
+        <v>3339.79</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.49</v>
+        <v>5.44</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1597,11 +1605,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>139.4</v>
+        <v>4.46</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1659,11 +1667,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>35.12</v>
+        <v>0</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1706,13 +1714,13 @@
         <v>4271.87</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1984.71</v>
+        <v>4271.87</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2287.16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46.46</v>
+        <v>100</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1721,11 +1729,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>2623.64</v>
+        <v>17.46</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1870,13 +1878,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9404.299999999999</v>
+        <v>13418.39</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>70513.25999999999</v>
+        <v>66499.17999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.77</v>
+        <v>16.79</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1885,11 +1893,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4014.08</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1951,7 +1959,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>14802.34</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2009,11 +2017,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1115.83</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2056,22 +2064,26 @@
         <v>23294.11</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>12208.1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23294.11</v>
+        <v>11086.01</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>52.41</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>12208.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2114,13 +2126,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4370.84</v>
+        <v>5153.26</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16301.02</v>
+        <v>15518.6</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21.14</v>
+        <v>24.93</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2129,11 +2141,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>944.8</v>
+        <v>681.52</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2176,13 +2188,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>488.32</v>
+        <v>1379.4</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7796.53</v>
+        <v>6905.45</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.89</v>
+        <v>16.65</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2191,11 +2203,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1070.02</v>
+        <v>813.62</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2253,7 +2265,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>2691.31</v>
+        <v>4775.15</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2311,11 +2323,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>310.27</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2358,22 +2370,26 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>20.85</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7414.97</v>
+        <v>7394.12</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>20.85</v>
+        <v>9.41</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2431,11 +2447,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>88.25</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2478,13 +2494,13 @@
         <v>5260.44</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44.96</v>
+        <v>308.02</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5215.48</v>
+        <v>4952.42</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.85</v>
+        <v>5.86</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2493,11 +2509,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>194.69</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2642,13 +2658,13 @@
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1844.77</v>
+        <v>1959.49</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3151.19</v>
+        <v>3036.47</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>36.93</v>
+        <v>39.22</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2657,11 +2673,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>135.59</v>
+        <v>27.69</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2766,13 +2782,13 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1142.98</v>
+        <v>1184.41</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5361.8</v>
+        <v>5320.37</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.57</v>
+        <v>18.21</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2781,11 +2797,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>41.44</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2828,13 +2844,13 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.06</v>
+        <v>40.97</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2378.79</v>
+        <v>2337.88</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2843,11 +2859,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>40.9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2952,22 +2968,26 @@
         <v>3431.79</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3431.79</v>
+        <v>3430.45</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3010,22 +3030,26 @@
         <v>3021.64</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3021.64</v>
+        <v>3015.31</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3126,13 +3150,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>104.29</v>
+        <v>143.85</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>468.03</v>
+        <v>428.47</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18.22</v>
+        <v>25.13</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3141,11 +3165,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>216.52</v>
+        <v>183.23</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3406,13 +3430,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4789.57</v>
+        <v>5111.13</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8456.65</v>
+        <v>8135.09</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>36.16</v>
+        <v>38.59</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3421,11 +3445,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>690.38</v>
+        <v>478.81</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3468,13 +3492,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>50.46</v>
+        <v>111.08</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10057.28</v>
+        <v>9996.66</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3483,11 +3507,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>49.98</v>
+        <v>20.23</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3530,13 +3554,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>410.3</v>
+        <v>831.04</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25060.74</v>
+        <v>24640</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.61</v>
+        <v>3.26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3545,11 +3569,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>576.41</v>
+        <v>642.46</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3592,22 +3616,26 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>1020.7</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17259.54</v>
+        <v>16238.84</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>1080.82</v>
+        <v>101.33</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3650,13 +3678,13 @@
         <v>13151.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5.14</v>
+        <v>45.56</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13146.5</v>
+        <v>13106.08</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3665,11 +3693,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>40.42</v>
+        <v>246.12</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3712,13 +3740,13 @@
         <v>10963.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.58</v>
+        <v>400.33</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10962.75</v>
+        <v>10563</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.01</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3727,11 +3755,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>399.75</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3774,13 +3802,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>806.3200000000001</v>
+        <v>894.9</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8707.120000000001</v>
+        <v>8618.540000000001</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8.48</v>
+        <v>9.41</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3789,11 +3817,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>88.09</v>
+        <v>123.34</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3894,13 +3922,13 @@
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2166.96</v>
+        <v>2556.83</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6275.61</v>
+        <v>5885.74</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25.67</v>
+        <v>30.28</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3909,11 +3937,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>543.39</v>
+        <v>466.92</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3956,13 +3984,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>69.77</v>
+        <v>84.31</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5484.48</v>
+        <v>5469.94</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3971,11 +3999,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>22.6</v>
+        <v>17.87</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4018,13 +4046,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>50.66</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>408.24</v>
+        <v>358.39</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.2</v>
+        <v>12.39</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4033,11 +4061,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>49.85</v>
+        <v>8.24</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4080,22 +4108,26 @@
         <v>31.27</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.27</v>
+        <v>30.75</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M13" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -4240,13 +4272,13 @@
         <v>928.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>20.84</v>
+        <v>34.24</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>907.65</v>
+        <v>894.25</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.24</v>
+        <v>3.69</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4255,11 +4287,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4538,13 +4570,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.86</v>
+        <v>16.14</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>269.52</v>
+        <v>255.24</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>5.95</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4553,11 +4585,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>24.51</v>
+        <v>12.02</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4760,13 +4792,13 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>23.53</v>
+        <v>70.61</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>502.5</v>
+        <v>455.42</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.47</v>
+        <v>13.42</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4775,11 +4807,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>47.08</v>
+        <v>22.94</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4837,11 +4869,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9.93</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5338,13 +5370,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>498.69</v>
+        <v>3587.3</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>66994.89</v>
+        <v>63906.28</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.74</v>
+        <v>5.32</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5353,11 +5385,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>3088.61</v>
+        <v>972.38</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5400,13 +5432,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6756.95</v>
+        <v>9843.99</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>56895.72</v>
+        <v>53808.68</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10.62</v>
+        <v>15.47</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5415,11 +5447,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3549.86</v>
+        <v>1374.57</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5462,13 +5494,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18305.08</v>
+        <v>26012.62</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>41847.83</v>
+        <v>34140.29</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>30.43</v>
+        <v>43.24</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5477,11 +5509,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>7707.53</v>
+        <v>277.51</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5524,13 +5556,13 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>102.24</v>
+        <v>204.73</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19732.39</v>
+        <v>19629.9</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.52</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -5539,11 +5571,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.25</v>
+        <v>5.84</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5648,13 +5680,13 @@
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>526.6900000000001</v>
+        <v>713.01</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26022.79</v>
+        <v>25836.47</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5663,11 +5695,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>186.32</v>
+        <v>5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5783,11 +5815,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>152.84</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5830,13 +5862,13 @@
         <v>21283.6</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>8086.14</v>
+        <v>13026.17</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13197.46</v>
+        <v>8257.43</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37.99</v>
+        <v>61.2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -5845,11 +5877,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>4265.86</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -5907,7 +5939,7 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1053.95</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -5950,22 +5982,26 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
+        <v>21.36</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>745.65</v>
+        <v>724.28</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M13" t="n">
-        <v>21.36</v>
+        <v>46.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6023,7 +6059,7 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>24.63</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -6738,22 +6774,26 @@
         <v>5166.66</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>711.2</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5166.66</v>
+        <v>4455.47</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>13.77</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>711.2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -6974,22 +7014,26 @@
         <v>1478.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1478.75</v>
+        <v>1478.59</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7265,11 +7309,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>419.11</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -7312,13 +7356,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>5040.46</v>
+        <v>7186.53</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21079.47</v>
+        <v>18933.4</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>19.3</v>
+        <v>27.51</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7327,11 +7371,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2146.07</v>
+        <v>185.87</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7374,13 +7418,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8065.13</v>
+        <v>10444.25</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>109431.79</v>
+        <v>107052.67</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.86</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7389,11 +7433,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2418.05</v>
+        <v>1560.22</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7451,11 +7495,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -7513,11 +7557,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>27.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -7560,13 +7604,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>58.36</v>
+        <v>14090.02</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>58237.49</v>
+        <v>44205.83</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.1</v>
+        <v>24.17</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7575,11 +7619,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>14828.94</v>
+        <v>2210.78</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7637,7 +7681,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>14098.39</v>
+        <v>29804.08</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7680,13 +7724,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.44</v>
+        <v>608.25</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11598.64</v>
+        <v>10991.83</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.01</v>
+        <v>5.24</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7695,11 +7739,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>592.72</v>
+        <v>300.11</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7804,13 +7848,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>645.9</v>
+        <v>2943.83</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2297.93</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21.94</v>
+        <v>100</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -7819,11 +7863,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>32.66</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -7928,13 +7972,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>5713.85</v>
+        <v>10998.75</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7047.47</v>
+        <v>1762.57</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>44.77</v>
+        <v>86.19</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -7943,11 +7987,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1493.6</v>
+        <v>4325.57</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -8092,13 +8136,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>18245.97</v>
+        <v>21324.17</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>92452.89</v>
+        <v>89374.69</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>16.48</v>
+        <v>19.26</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8107,11 +8151,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3353.77</v>
+        <v>1569.47</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8169,11 +8213,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>74.22</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -8216,13 +8260,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>138.84</v>
+        <v>324.72</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34163.49</v>
+        <v>33977.61</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4</v>
+        <v>0.95</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8231,11 +8275,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>130.96</v>
+        <v>247.95</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8293,11 +8337,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>993.03</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -8340,13 +8384,13 @@
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>6145.08</v>
+        <v>16393.13</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19365.83</v>
+        <v>9117.77</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24.09</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8355,11 +8399,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>10248.05</v>
+        <v>0.12</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8417,7 +8461,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>381.56</v>
+        <v>974.63</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8460,13 +8504,13 @@
         <v>23174.68</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>15714.62</v>
+        <v>16576.7</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7460.06</v>
+        <v>6597.98</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>67.81</v>
+        <v>71.53</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8475,11 +8519,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>885.92</v>
+        <v>1786.79</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8522,13 +8566,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10330.59</v>
+        <v>10518.27</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12254.58</v>
+        <v>12066.9</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45.74</v>
+        <v>46.57</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8537,11 +8581,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>173.51</v>
+        <v>110.58</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8584,13 +8628,13 @@
         <v>1878.7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>19.93</v>
+        <v>27.51</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1858.77</v>
+        <v>1851.19</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -8599,11 +8643,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>7.57</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8646,13 +8690,13 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>132.31</v>
+        <v>231.04</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>182.16</v>
+        <v>83.44</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>42.07</v>
+        <v>73.47</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8661,11 +8705,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>98.72</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8810,26 +8854,26 @@
         <v>54334.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>48005.59</v>
+        <v>52742.53</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6328.84</v>
+        <v>1591.9</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>88.34999999999999</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8464.27</v>
+        <v>3727.33</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8872,13 +8916,13 @@
         <v>41828.13</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>39180.29</v>
+        <v>41329.14</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2647.84</v>
+        <v>498.99</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>93.67</v>
+        <v>98.81</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -8887,11 +8931,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2258.45</v>
+        <v>298.43</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9011,11 +9055,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -9073,11 +9117,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>22.02</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -9120,13 +9164,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>21.16</v>
+        <v>906.12</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7973.98</v>
+        <v>7089.02</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.26</v>
+        <v>11.33</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9135,11 +9179,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>968.61</v>
+        <v>255.65</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9197,7 +9241,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>423.75</v>
+        <v>2347.52</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9240,13 +9284,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3406.36</v>
+        <v>3766.28</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3561.73</v>
+        <v>3201.81</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48.89</v>
+        <v>54.05</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9255,11 +9299,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1616.88</v>
+        <v>1256.96</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9302,13 +9346,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2.74</v>
+        <v>34.64</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1934.93</v>
+        <v>1903.03</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.14</v>
+        <v>1.79</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9317,11 +9361,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>31.9</v>
+        <v>0.11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9364,13 +9408,13 @@
         <v>1831.54</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1723.05</v>
+        <v>1747.44</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>108.5</v>
+        <v>84.09</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>94.08</v>
+        <v>95.41</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -9379,11 +9423,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9528,13 +9572,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>107.78</v>
+        <v>393.18</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>38244.43</v>
+        <v>37959.03</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.28</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9543,11 +9587,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>285.4</v>
+        <v>7004.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9590,13 +9634,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>132.55</v>
+        <v>276.58</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15078.51</v>
+        <v>14934.48</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.87</v>
+        <v>1.82</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9605,11 +9649,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>282.95</v>
+        <v>440.28</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9652,13 +9696,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>130.3</v>
+        <v>491.74</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15487.72</v>
+        <v>15126.28</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.83</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9667,11 +9711,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>418.87</v>
+        <v>302.05</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9714,22 +9758,26 @@
         <v>14278.53</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14278.53</v>
+        <v>13255.53</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>7.16</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>1023</v>
+        <v>2.09</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -9772,22 +9820,26 @@
         <v>13880.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>775.71</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13880.42</v>
+        <v>13104.71</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M6" t="n">
-        <v>848.36</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -9961,11 +10013,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>07-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>843.41</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -10008,22 +10060,26 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5977.74</v>
+        <v>5967.74</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>07-10-2026</t>
+        </is>
+      </c>
       <c r="M10" t="n">
-        <v>132.81</v>
+        <v>1353.71</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -676,13 +676,13 @@
         <v>149318.61</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>130192.57</v>
+        <v>149318.61</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19126.04</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>87.19</v>
+        <v>100</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -691,11 +691,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>23628.14</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>324.14</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -858,13 +858,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>8463.450000000001</v>
+        <v>8483.6</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>106994.07</v>
+        <v>106973.92</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.33</v>
+        <v>7.35</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -873,11 +873,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2295.44</v>
+        <v>2288.87</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>23986.23</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2445.44</v>
+        <v>2623.97</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>62078.21</v>
+        <v>61899.68</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.79</v>
+        <v>4.07</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1059,11 +1059,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>198.52</v>
+        <v>940.38</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>194001.02</v>
+        <v>210269.27</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>23.26</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>133.82</v>
+        <v>134.15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38347.32</v>
+        <v>38346.99</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.35</v>
@@ -1241,11 +1241,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>16.42</v>
+        <v>44.49</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>7.85</v>
+        <v>7.87</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5464.65</v>
+        <v>5464.63</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.14</v>
@@ -1485,11 +1485,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>10.47</v>
+        <v>15.23</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>192.12</v>
+        <v>194.66</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3339.79</v>
+        <v>3337.25</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.44</v>
+        <v>5.51</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1605,11 +1605,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4.46</v>
+        <v>50.95</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -1878,13 +1878,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>13418.39</v>
+        <v>13699.44</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>66499.17999999999</v>
+        <v>66218.12</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>16.79</v>
+        <v>17.14</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1893,11 +1893,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>10.01</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1940,13 +1940,13 @@
         <v>53152.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4488.84</v>
+        <v>19291.18</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>48663.74</v>
+        <v>33861.4</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>36.29</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>14802.34</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5153.26</v>
+        <v>5693.82</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15518.6</v>
+        <v>14978.04</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24.93</v>
+        <v>27.54</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2141,11 +2141,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>681.52</v>
+        <v>589.9299999999999</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2188,13 +2188,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1379.4</v>
+        <v>1664.62</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6905.45</v>
+        <v>6620.23</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16.65</v>
+        <v>20.09</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2203,11 +2203,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>813.62</v>
+        <v>891.98</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>4775.15</v>
+        <v>10121.16</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2370,13 +2370,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>20.85</v>
+        <v>28.66</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7394.12</v>
+        <v>7386.31</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2385,11 +2385,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>9.41</v>
+        <v>4.21</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -2658,13 +2658,13 @@
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1959.49</v>
+        <v>1987.18</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3036.47</v>
+        <v>3008.78</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>39.22</v>
+        <v>39.78</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2673,11 +2673,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>27.69</v>
+        <v>13.99</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2844,13 +2844,13 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>40.97</v>
+        <v>50.33</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2337.88</v>
+        <v>2328.52</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2859,11 +2859,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9.359999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3150,13 +3150,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>143.85</v>
+        <v>320.9</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>428.47</v>
+        <v>251.42</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25.13</v>
+        <v>56.07</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3165,11 +3165,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>183.23</v>
+        <v>28.16</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3430,13 +3430,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5111.13</v>
+        <v>5549.3</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8135.09</v>
+        <v>7696.92</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>38.59</v>
+        <v>41.89</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3445,11 +3445,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>478.81</v>
+        <v>102.45</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3492,13 +3492,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>111.08</v>
+        <v>129.19</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9996.66</v>
+        <v>9978.549999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3507,11 +3507,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>20.23</v>
+        <v>2.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3554,13 +3554,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>831.04</v>
+        <v>1026.42</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>24640</v>
+        <v>24444.62</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.26</v>
+        <v>4.03</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3569,11 +3569,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>642.46</v>
+        <v>522.13</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3616,13 +3616,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1020.7</v>
+        <v>1143.46</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16238.84</v>
+        <v>16116.08</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.91</v>
+        <v>6.63</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3631,11 +3631,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>101.33</v>
+        <v>448.35</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3678,13 +3678,13 @@
         <v>13151.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45.56</v>
+        <v>259.02</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13106.08</v>
+        <v>12892.62</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.35</v>
+        <v>1.97</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3693,11 +3693,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>246.12</v>
+        <v>32.72</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>894.9</v>
+        <v>894.91</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8618.540000000001</v>
+        <v>8618.530000000001</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>9.41</v>
@@ -3817,11 +3817,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>123.34</v>
+        <v>164.68</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3922,13 +3922,13 @@
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2556.83</v>
+        <v>2726.27</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5885.74</v>
+        <v>5716.3</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>30.28</v>
+        <v>32.29</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3937,11 +3937,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>466.92</v>
+        <v>412.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3984,13 +3984,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>84.31</v>
+        <v>102.17</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5469.94</v>
+        <v>5452.08</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3999,11 +3999,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>17.87</v>
+        <v>37.95</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4046,13 +4046,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>50.66</v>
+        <v>58.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>358.39</v>
+        <v>350.15</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12.39</v>
+        <v>14.4</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4061,11 +4061,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>8.24</v>
+        <v>12.2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4570,13 +4570,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>16.14</v>
+        <v>26.37</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>255.24</v>
+        <v>245.01</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.95</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4585,11 +4585,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>12.02</v>
+        <v>5.75</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4916,13 +4916,13 @@
         <v>243.93</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>16.41</v>
+        <v>43.97</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>227.52</v>
+        <v>199.96</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.73</v>
+        <v>18.03</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4931,11 +4931,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>27.56</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5432,13 +5432,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9843.99</v>
+        <v>10306.81</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>53808.68</v>
+        <v>53345.86</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15.47</v>
+        <v>16.19</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5447,11 +5447,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1374.57</v>
+        <v>1496.47</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5494,13 +5494,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>26012.62</v>
+        <v>26201.65</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34140.29</v>
+        <v>33951.26</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43.24</v>
+        <v>43.56</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5509,11 +5509,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>277.51</v>
+        <v>3517.05</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5556,13 +5556,13 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>204.73</v>
+        <v>209.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19629.9</v>
+        <v>19625.06</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -5571,11 +5571,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>5.84</v>
+        <v>36.25</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>155.29</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -5862,13 +5862,13 @@
         <v>21283.6</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>13026.17</v>
+        <v>13106.42</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>8257.43</v>
+        <v>8177.18</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>61.2</v>
+        <v>61.58</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -5924,22 +5924,26 @@
         <v>1294.54</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>1053.96</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1294.54</v>
+        <v>240.58</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>81.42</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>08-10-2026</t>
+        </is>
+      </c>
       <c r="M12" t="n">
-        <v>1053.95</v>
+        <v>27.82</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -5982,13 +5986,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>21.36</v>
+        <v>65.37</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>724.28</v>
+        <v>680.28</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.87</v>
+        <v>8.77</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -5997,11 +6001,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>46.5</v>
+        <v>100.87</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6044,22 +6048,26 @@
         <v>3533.82</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>11.27</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3533.82</v>
+        <v>3522.55</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>08-10-2026</t>
+        </is>
+      </c>
       <c r="M14" t="n">
-        <v>24.63</v>
+        <v>24.54</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -7014,13 +7022,13 @@
         <v>1478.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.16</v>
+        <v>2.18</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1478.59</v>
+        <v>1476.57</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7029,11 +7037,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7356,13 +7364,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7186.53</v>
+        <v>7213.9</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18933.4</v>
+        <v>18906.03</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>27.51</v>
+        <v>27.62</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7371,11 +7379,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>185.87</v>
+        <v>348.35</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7418,13 +7426,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10444.25</v>
+        <v>10483.18</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>107052.67</v>
+        <v>107013.74</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7433,11 +7441,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1560.22</v>
+        <v>3290.78</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7604,13 +7612,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>14090.02</v>
+        <v>14913.02</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44205.83</v>
+        <v>43382.83</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>24.17</v>
+        <v>25.58</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7619,11 +7627,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2210.78</v>
+        <v>1417.65</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7681,7 +7689,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>29804.08</v>
+        <v>30660.52</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7724,13 +7732,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>608.25</v>
+        <v>719.36</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10991.83</v>
+        <v>10880.72</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.24</v>
+        <v>6.2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7739,11 +7747,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>300.11</v>
+        <v>505.56</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7972,13 +7980,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>10998.75</v>
+        <v>11022.2</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1762.57</v>
+        <v>1739.12</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>86.19</v>
+        <v>86.37</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -7987,11 +7995,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4325.57</v>
+        <v>4325.7</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -8136,13 +8144,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>21324.17</v>
+        <v>21599.73</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>89374.69</v>
+        <v>89099.13</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19.26</v>
+        <v>19.51</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8151,11 +8159,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1569.47</v>
+        <v>1304.43</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8260,13 +8268,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>324.72</v>
+        <v>430.11</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33977.61</v>
+        <v>33872.22</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.95</v>
+        <v>1.25</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8275,11 +8283,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>247.95</v>
+        <v>212.97</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8384,10 +8392,10 @@
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>16393.13</v>
+        <v>16393.26</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9117.77</v>
+        <v>9117.65</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>64.26000000000001</v>
@@ -8399,11 +8407,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8461,7 +8469,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>974.63</v>
+        <v>1069.79</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8504,13 +8512,13 @@
         <v>23174.68</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>16576.7</v>
+        <v>16660.92</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6597.98</v>
+        <v>6513.76</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>71.53</v>
+        <v>71.89</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8519,11 +8527,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1786.79</v>
+        <v>1805.22</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8566,13 +8574,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10518.27</v>
+        <v>10605.46</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12066.9</v>
+        <v>11979.71</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46.57</v>
+        <v>46.96</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8581,11 +8589,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>110.58</v>
+        <v>111.46</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8690,10 +8698,10 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>231.04</v>
+        <v>231.05</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>83.44</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>73.47</v>
@@ -8705,7 +8713,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -8854,13 +8862,13 @@
         <v>54334.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>52742.53</v>
+        <v>54334.43</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1591.9</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>100</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8869,11 +8877,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3727.33</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8916,13 +8924,13 @@
         <v>41828.13</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>41329.14</v>
+        <v>41626.39</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>498.99</v>
+        <v>201.74</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>98.81</v>
+        <v>99.52</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -8931,11 +8939,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>298.43</v>
+        <v>1.18</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9164,13 +9172,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>906.12</v>
+        <v>1050.16</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7089.02</v>
+        <v>6944.98</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11.33</v>
+        <v>13.13</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9179,11 +9187,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>255.65</v>
+        <v>167.46</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9241,7 +9249,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>2347.52</v>
+        <v>3892.21</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9284,13 +9292,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3766.28</v>
+        <v>5023.24</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3201.81</v>
+        <v>1944.85</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>54.05</v>
+        <v>72.09</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9299,11 +9307,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1256.96</v>
+        <v>82.92</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9361,7 +9369,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -9572,13 +9580,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>393.18</v>
+        <v>461.85</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>37959.03</v>
+        <v>37890.35</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9587,11 +9595,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7004.5</v>
+        <v>7085.81</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9634,13 +9642,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>276.58</v>
+        <v>484.9</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14934.48</v>
+        <v>14726.16</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.82</v>
+        <v>3.19</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9649,11 +9657,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>440.28</v>
+        <v>353.95</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9696,13 +9704,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>491.74</v>
+        <v>657.11</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15126.28</v>
+        <v>14960.91</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.15</v>
+        <v>4.21</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9711,11 +9719,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>302.05</v>
+        <v>362.76</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9758,13 +9766,13 @@
         <v>14278.53</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1023</v>
+        <v>1025.09</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>13255.53</v>
+        <v>13253.44</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.16</v>
+        <v>7.18</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -9773,11 +9781,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -9820,13 +9828,13 @@
         <v>13880.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>775.71</v>
+        <v>848.36</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13104.71</v>
+        <v>13032.06</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.59</v>
+        <v>6.11</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -9835,11 +9843,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>72.65000000000001</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -10060,13 +10068,13 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10</v>
+        <v>1038.04</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5967.74</v>
+        <v>4939.7</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.17</v>
+        <v>17.37</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -10075,11 +10083,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>08-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1353.71</v>
+        <v>368.54</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>69.84</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>9657.690000000001</v>
+        <v>9657.84</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>324.14</v>
+        <v>483.33</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2288.87</v>
+        <v>2624.45</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>23986.23</v>
+        <v>23986.46</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>940.38</v>
+        <v>2044.12</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>210269.27</v>
+        <v>266159.77</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>23.26</v>
+        <v>50.88</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>44.49</v>
+        <v>135.12</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>321.23</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>15.23</v>
+        <v>21.32</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>50.95</v>
+        <v>408.07</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>10.01</v>
+        <v>597.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>589.9299999999999</v>
+        <v>2484</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>891.98</v>
+        <v>1226.07</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>10121.16</v>
+        <v>10541.96</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4.21</v>
+        <v>6.34</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>13.99</v>
+        <v>27.76</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.17</v>
+        <v>460.51</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>28.16</v>
+        <v>43.79</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>102.45</v>
+        <v>166.71</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2.3</v>
+        <v>6.12</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>522.13</v>
+        <v>1734.36</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>448.35</v>
+        <v>548.22</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32.72</v>
+        <v>42.69</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>164.68</v>
+        <v>182.6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>412.9</v>
+        <v>435.57</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>37.95</v>
+        <v>106.78</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>22.94</v>
+        <v>32.75</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>972.38</v>
+        <v>11933.38</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1496.47</v>
+        <v>2906.21</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3517.05</v>
+        <v>3634</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>36.25</v>
+        <v>37.33</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>155.29</v>
+        <v>177.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1664.25</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>100.87</v>
+        <v>176.37</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>24.54</v>
+        <v>39.91</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>348.35</v>
+        <v>376.04</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3290.78</v>
+        <v>3303.11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1417.65</v>
+        <v>3854.53</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>30660.52</v>
+        <v>35495.24</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>505.56</v>
+        <v>1070.09</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4325.7</v>
+        <v>4333.61</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1304.43</v>
+        <v>5811.95</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>212.97</v>
+        <v>345.75</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2911.58</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>1069.79</v>
+        <v>1194.67</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1805.22</v>
+        <v>3670.11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2567.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>167.46</v>
+        <v>289.02</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>3892.21</v>
+        <v>6493</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>82.92</v>
+        <v>105.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.11</v>
+        <v>1.71</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7085.81</v>
+        <v>7627.69</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>353.95</v>
+        <v>399.78</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>362.76</v>
+        <v>542.38</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2590.02</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,11 +571,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>69.84</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -738,22 +738,26 @@
         <v>69730.64</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>9657.690000000001</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>69730.64</v>
+        <v>60072.94</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>13.85</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>12-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>9657.84</v>
+        <v>0.14</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -796,13 +800,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>481.4</v>
+        <v>964.73</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>120400.95</v>
+        <v>119917.62</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -811,11 +815,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>483.33</v>
+        <v>1506.51</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -858,13 +862,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>8483.6</v>
+        <v>10775.93</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>106973.92</v>
+        <v>104681.59</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.35</v>
+        <v>9.33</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -873,11 +877,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2624.45</v>
+        <v>332.12</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -920,13 +924,13 @@
         <v>103743.08</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55407.72</v>
+        <v>79393.95</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>48335.36</v>
+        <v>24349.13</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>53.41</v>
+        <v>76.53</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -935,11 +939,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>23986.46</v>
+        <v>0.23</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -982,13 +986,13 @@
         <v>101232.21</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4885.32</v>
+        <v>24858.97</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>96346.89</v>
+        <v>76373.24000000001</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.83</v>
+        <v>24.56</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -997,11 +1001,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19973.65</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1044,13 +1048,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2623.97</v>
+        <v>4647.97</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>61899.68</v>
+        <v>59875.68</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.07</v>
+        <v>7.2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1059,11 +1063,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2044.12</v>
+        <v>720.04</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>266159.77</v>
+        <v>272439.27</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1164,13 +1168,13 @@
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>39.49</v>
+        <v>62.75</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42473.26</v>
+        <v>42450</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1179,11 +1183,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>50.88</v>
+        <v>47.34</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1226,13 +1230,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>134.15</v>
+        <v>228.79</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38346.99</v>
+        <v>38252.35</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1241,11 +1245,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>135.12</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1470,13 +1474,13 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>7.87</v>
+        <v>23.33</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5464.63</v>
+        <v>5449.17</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1485,11 +1489,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>21.32</v>
+        <v>6.37</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1590,13 +1594,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>194.66</v>
+        <v>602.73</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3337.25</v>
+        <v>2929.18</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.51</v>
+        <v>17.07</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1605,11 +1609,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>408.07</v>
+        <v>114.77</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1667,7 +1671,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -1729,11 +1733,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>17.46</v>
+        <v>0</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1878,13 +1882,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>13699.44</v>
+        <v>14296.74</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>66218.12</v>
+        <v>65620.82000000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17.14</v>
+        <v>17.89</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1893,11 +1897,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>597.3</v>
+        <v>4980.15</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2126,13 +2130,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5693.82</v>
+        <v>8155.21</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14978.04</v>
+        <v>12516.65</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27.54</v>
+        <v>39.45</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2141,11 +2145,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2484</v>
+        <v>459.1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2188,13 +2192,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1664.62</v>
+        <v>2556.6</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6620.23</v>
+        <v>5728.25</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20.09</v>
+        <v>30.86</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2203,11 +2207,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1226.07</v>
+        <v>841.86</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2265,7 +2269,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>10541.96</v>
+        <v>10961.73</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2370,13 +2374,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>28.66</v>
+        <v>32.87</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7386.31</v>
+        <v>7382.1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2385,11 +2389,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>6.34</v>
+        <v>31.11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2494,13 +2498,13 @@
         <v>5260.44</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>308.02</v>
+        <v>512.29</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4952.42</v>
+        <v>4748.15</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5.86</v>
+        <v>9.74</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2509,7 +2513,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -2658,13 +2662,13 @@
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1987.18</v>
+        <v>2014.93</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3008.78</v>
+        <v>2981.03</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>39.78</v>
+        <v>40.33</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2673,11 +2677,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>27.76</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2720,13 +2724,13 @@
         <v>8960.700000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>5.24</v>
+        <v>8.93</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8955.459999999999</v>
+        <v>8951.77</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2735,11 +2739,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>3.69</v>
+        <v>0.49</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2782,10 +2786,10 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1184.41</v>
+        <v>1184.58</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5320.37</v>
+        <v>5320.2</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>18.21</v>
@@ -2797,11 +2801,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>460.51</v>
+        <v>460.33</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2844,13 +2848,13 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>50.33</v>
+        <v>58.43</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2328.52</v>
+        <v>2320.42</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2859,11 +2863,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>8.1</v>
+        <v>2.4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2925,7 +2929,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1575.44</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3049,7 +3053,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>211.76</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3150,13 +3154,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>320.9</v>
+        <v>364.18</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>251.42</v>
+        <v>208.14</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>56.07</v>
+        <v>63.63</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3165,11 +3169,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>43.79</v>
+        <v>12.24</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3225,7 +3229,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>12-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -3430,13 +3438,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5549.3</v>
+        <v>5714.76</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7696.92</v>
+        <v>7531.46</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>41.89</v>
+        <v>43.14</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3445,11 +3453,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>166.71</v>
+        <v>436.48</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3492,13 +3500,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>129.19</v>
+        <v>134.4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9978.549999999999</v>
+        <v>9973.34</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3507,11 +3515,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>6.12</v>
+        <v>24.66</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3554,13 +3562,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1026.42</v>
+        <v>1582.93</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>24444.62</v>
+        <v>23888.11</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.03</v>
+        <v>6.21</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3569,11 +3577,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1734.36</v>
+        <v>2453.36</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3616,13 +3624,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1143.46</v>
+        <v>1688.43</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16116.08</v>
+        <v>15571.11</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6.63</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3631,11 +3639,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>548.22</v>
+        <v>348.99</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3678,13 +3686,13 @@
         <v>13151.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>259.02</v>
+        <v>291.74</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12892.62</v>
+        <v>12859.9</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3693,11 +3701,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>42.69</v>
+        <v>286.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3759,7 +3767,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>375.06</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3802,13 +3810,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>894.91</v>
+        <v>1077.51</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8618.530000000001</v>
+        <v>8435.93</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.41</v>
+        <v>11.33</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3817,11 +3825,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>182.6</v>
+        <v>22.18</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3922,13 +3930,13 @@
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2726.27</v>
+        <v>3144.18</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5716.3</v>
+        <v>5298.39</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>32.29</v>
+        <v>37.24</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3937,11 +3945,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>435.57</v>
+        <v>82.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3984,13 +3992,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>102.17</v>
+        <v>148.93</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5452.08</v>
+        <v>5405.32</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.84</v>
+        <v>2.68</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3999,11 +4007,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>106.78</v>
+        <v>84.72</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4046,13 +4054,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.9</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>350.15</v>
+        <v>337.95</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14.4</v>
+        <v>17.38</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4061,11 +4069,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>12.2</v>
+        <v>5.96</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4108,13 +4116,13 @@
         <v>31.27</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.75</v>
+        <v>30.72</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -4123,7 +4131,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -4291,7 +4299,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4570,13 +4578,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>26.37</v>
+        <v>32.12</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>245.01</v>
+        <v>239.26</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>11.84</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4585,11 +4593,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4792,13 +4800,13 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.61</v>
+        <v>93.55</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>455.42</v>
+        <v>432.48</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>13.42</v>
+        <v>17.78</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4807,11 +4815,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>32.75</v>
+        <v>9.81</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5312,22 +5320,26 @@
         <v>33586.54</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33586.54</v>
+        <v>33584.46</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>12-10-2026</t>
+        </is>
+      </c>
       <c r="M2" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5370,13 +5382,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3587.3</v>
+        <v>4694</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>63906.28</v>
+        <v>62799.58</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5.32</v>
+        <v>6.95</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5385,11 +5397,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11933.38</v>
+        <v>12048.14</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5432,13 +5444,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10306.81</v>
+        <v>12472.72</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>53345.86</v>
+        <v>51179.95</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.19</v>
+        <v>19.59</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5447,11 +5459,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2906.21</v>
+        <v>740.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5494,13 +5506,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>26201.65</v>
+        <v>29835.65</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33951.26</v>
+        <v>30317.26</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43.56</v>
+        <v>49.6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5509,11 +5521,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3634</v>
+        <v>100.78</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5556,13 +5568,13 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>209.57</v>
+        <v>246.9</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19625.06</v>
+        <v>19587.73</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -5571,11 +5583,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>37.33</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5618,10 +5630,10 @@
         <v>29457.81</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29457.79</v>
+        <v>29457.72</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -5633,11 +5645,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5680,13 +5692,13 @@
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>713.01</v>
+        <v>890.51</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25836.47</v>
+        <v>25658.97</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.69</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5695,11 +5707,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>177.5</v>
+        <v>21.26</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5862,13 +5874,13 @@
         <v>21283.6</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>13106.42</v>
+        <v>14770.67</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>8177.18</v>
+        <v>6512.93</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>61.58</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -5877,11 +5889,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1664.25</v>
+        <v>2503.71</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -5924,13 +5936,13 @@
         <v>1294.54</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1053.96</v>
+        <v>1081.77</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>240.58</v>
+        <v>212.77</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>81.42</v>
+        <v>83.56</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -5939,11 +5951,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -5986,13 +5998,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>65.37</v>
+        <v>169.69</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>680.28</v>
+        <v>575.97</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8.77</v>
+        <v>22.76</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6001,11 +6013,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>176.37</v>
+        <v>124.31</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6048,13 +6060,13 @@
         <v>3533.82</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>11.27</v>
+        <v>51.18</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3522.55</v>
+        <v>3482.64</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.32</v>
+        <v>1.45</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -6063,11 +6075,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>39.91</v>
+        <v>1.43</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -6863,7 +6875,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2491.72</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7364,13 +7376,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7213.9</v>
+        <v>7589.94</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18906.03</v>
+        <v>18529.99</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>27.62</v>
+        <v>29.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7379,11 +7391,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>376.04</v>
+        <v>172.64</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7426,13 +7438,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>10483.18</v>
+        <v>13786.28</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>107013.74</v>
+        <v>103710.64</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8.92</v>
+        <v>11.73</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7441,11 +7453,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3303.11</v>
+        <v>4853.23</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7612,13 +7624,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>14913.02</v>
+        <v>19513.67</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>43382.83</v>
+        <v>38782.18</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25.58</v>
+        <v>33.47</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7627,11 +7639,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3854.53</v>
+        <v>5512.18</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7732,13 +7744,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>719.36</v>
+        <v>1366.51</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10880.72</v>
+        <v>10233.57</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6.2</v>
+        <v>11.78</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7747,11 +7759,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1070.09</v>
+        <v>787.27</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7980,13 +7992,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>11022.2</v>
+        <v>12761.32</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1739.12</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>86.37</v>
+        <v>100</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -7995,11 +8007,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4333.61</v>
+        <v>29.34</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -8144,13 +8156,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>21599.73</v>
+        <v>26270.83</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>89099.13</v>
+        <v>84428.03</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19.51</v>
+        <v>23.73</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8159,11 +8171,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>5811.95</v>
+        <v>5803.31</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8268,13 +8280,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>430.11</v>
+        <v>679.29</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33872.22</v>
+        <v>33623.04</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8283,11 +8295,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>345.75</v>
+        <v>208.49</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8411,7 +8423,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2911.58</v>
+        <v>3169.46</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8469,7 +8481,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>1194.67</v>
+        <v>2050.42</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8512,13 +8524,13 @@
         <v>23174.68</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>16660.92</v>
+        <v>20329.54</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6513.76</v>
+        <v>2845.14</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>71.89</v>
+        <v>87.72</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8527,11 +8539,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3670.11</v>
+        <v>433.48</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8574,13 +8586,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10605.46</v>
+        <v>10716.92</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11979.71</v>
+        <v>11868.25</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46.96</v>
+        <v>47.45</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8589,11 +8601,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>111.46</v>
+        <v>61.33</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8717,7 +8729,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>15.7</v>
+        <v>24.12</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8877,11 +8889,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2567.2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8924,10 +8936,10 @@
         <v>41828.13</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>41626.39</v>
+        <v>41627.58</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>201.74</v>
+        <v>200.55</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>99.52</v>
@@ -8939,11 +8951,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1.18</v>
+        <v>363.99</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9005,7 +9017,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9172,13 +9184,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1050.16</v>
+        <v>1288.48</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6944.98</v>
+        <v>6706.66</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.13</v>
+        <v>16.12</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9187,11 +9199,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>289.02</v>
+        <v>238.34</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9249,7 +9261,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>6493</v>
+        <v>6549.3</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9292,13 +9304,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5023.24</v>
+        <v>5124</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1944.85</v>
+        <v>1844.09</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>72.09</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9307,11 +9319,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>105.8</v>
+        <v>168.47</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9354,13 +9366,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>34.64</v>
+        <v>36.35</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1903.03</v>
+        <v>1901.32</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9369,11 +9381,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9580,13 +9592,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>461.85</v>
+        <v>7635.43</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>37890.35</v>
+        <v>30716.77</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.2</v>
+        <v>19.91</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9595,11 +9607,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7627.69</v>
+        <v>501.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9642,13 +9654,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>484.9</v>
+        <v>884.6799999999999</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14726.16</v>
+        <v>14326.38</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.19</v>
+        <v>5.82</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9657,11 +9669,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>399.78</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9704,13 +9716,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>657.11</v>
+        <v>1062.62</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14960.91</v>
+        <v>14555.4</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.21</v>
+        <v>6.8</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9719,11 +9731,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>542.38</v>
+        <v>293.17</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9905,7 +9917,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>533.33</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -10068,13 +10080,13 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1038.04</v>
+        <v>1406.57</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4939.7</v>
+        <v>4571.17</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17.37</v>
+        <v>23.53</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -10083,11 +10095,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>12-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>368.54</v>
+        <v>42.54</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1506.51</v>
+        <v>1530.55</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>332.12</v>
+        <v>29460.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.23</v>
+        <v>10632.34</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>720.04</v>
+        <v>2463.33</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>272439.27</v>
+        <v>300771.78</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>47.34</v>
+        <v>67.05</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>88.73999999999999</v>
+        <v>195.81</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>6.37</v>
+        <v>17.68</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>114.77</v>
+        <v>252.43</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>459.1</v>
+        <v>1280.34</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>841.86</v>
+        <v>1106.82</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>132.07</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>31.11</v>
+        <v>169.63</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>20.91</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.4</v>
+        <v>91.81</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>12.24</v>
+        <v>44.87</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>436.48</v>
+        <v>478.01</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>24.66</v>
+        <v>92.33</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2453.36</v>
+        <v>3213.76</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>348.99</v>
+        <v>512.6799999999999</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>22.18</v>
+        <v>123.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>82.2</v>
+        <v>248.53</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>84.72</v>
+        <v>118.22</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>5.96</v>
+        <v>29.21</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9.81</v>
+        <v>23.19</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>12048.14</v>
+        <v>15272.27</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>740.3</v>
+        <v>3685.86</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>100.78</v>
+        <v>559.86</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>8.27</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>21.26</v>
+        <v>118.26</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>34.69</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>2503.71</v>
+        <v>3598.54</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>24.15</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>124.31</v>
+        <v>146.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>172.64</v>
+        <v>1264.15</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4853.23</v>
+        <v>5053.59</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5512.18</v>
+        <v>6668.13</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>787.27</v>
+        <v>1481.26</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>29.34</v>
+        <v>33.24</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>5803.31</v>
+        <v>7925.03</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>208.49</v>
+        <v>372.13</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>3169.46</v>
+        <v>4309.55</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>2050.42</v>
+        <v>2081.07</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>433.48</v>
+        <v>605.87</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>61.33</v>
+        <v>154.07</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>24.12</v>
+        <v>24.15</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>363.99</v>
+        <v>658.46</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>238.34</v>
+        <v>341.09</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>6549.3</v>
+        <v>10056.14</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>168.47</v>
+        <v>293.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>501.5</v>
+        <v>552.14</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>92.59999999999999</v>
+        <v>320.46</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>293.17</v>
+        <v>504.74</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>533.33</v>
+        <v>4979.22</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1530.55</v>
+        <v>1549.43</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10632.34</v>
+        <v>10632.7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>14.27</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2463.33</v>
+        <v>2610.41</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>300771.78</v>
+        <v>300771.79</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>67.05</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>195.81</v>
+        <v>196.73</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>17.68</v>
+        <v>39.15</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>252.43</v>
+        <v>307.04</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4980.15</v>
+        <v>9253.32</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1280.34</v>
+        <v>1662.21</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1106.82</v>
+        <v>1353.31</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>169.63</v>
+        <v>173.23</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>91.81</v>
+        <v>104.18</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>44.87</v>
+        <v>56.02</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>478.01</v>
+        <v>489.33</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>92.33</v>
+        <v>93.28</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3213.76</v>
+        <v>3489.71</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>512.6799999999999</v>
+        <v>536.54</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>123.4</v>
+        <v>238.69</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>248.53</v>
+        <v>386.14</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>118.22</v>
+        <v>159.28</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>29.21</v>
+        <v>35.6</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>15272.27</v>
+        <v>17500.06</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3685.86</v>
+        <v>3706.66</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>559.86</v>
+        <v>981.25</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8.27</v>
+        <v>26.51</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>12</v>
+        <v>16.48</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>118.26</v>
+        <v>158.93</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.69</v>
+        <v>1243.43</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3598.54</v>
+        <v>4560.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>146.6</v>
+        <v>147.2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1264.15</v>
+        <v>1778.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>5053.59</v>
+        <v>8191.15</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>6668.13</v>
+        <v>7004.27</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1481.26</v>
+        <v>1850.71</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7925.03</v>
+        <v>7928.26</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>372.13</v>
+        <v>468.01</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4309.55</v>
+        <v>4310.69</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>2081.07</v>
+        <v>2097.23</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>605.87</v>
+        <v>657.01</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>154.07</v>
+        <v>178.07</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>24.15</v>
+        <v>28.23</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>658.46</v>
+        <v>677.11</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>341.09</v>
+        <v>480.41</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.62</v>
+        <v>5.17</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>552.14</v>
+        <v>599.01</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>504.74</v>
+        <v>622.26</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -618,10 +618,10 @@
         <v>137884.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>137884.78</v>
+        <v>137884.46</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -631,9 +631,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,10 +742,10 @@
         <v>69730.64</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9657.690000000001</v>
+        <v>9657.84</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>60072.94</v>
+        <v>60072.8</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>13.85</v>
@@ -753,11 +757,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -800,13 +804,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>964.73</v>
+        <v>2514.16</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>119917.62</v>
+        <v>118368.19</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.8</v>
+        <v>2.08</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -815,11 +819,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1549.43</v>
+        <v>964.86</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -862,13 +866,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10775.93</v>
+        <v>40236.23</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>104681.59</v>
+        <v>75221.28999999999</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.33</v>
+        <v>34.85</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -877,11 +881,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>29460.3</v>
+        <v>5.92</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -924,13 +928,13 @@
         <v>103743.08</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>79393.95</v>
+        <v>90026.64</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24349.13</v>
+        <v>13716.44</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>76.53</v>
+        <v>86.78</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -939,11 +943,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10632.7</v>
+        <v>56.15</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -986,13 +990,13 @@
         <v>101232.21</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>24858.97</v>
+        <v>24873.24</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>76373.24000000001</v>
+        <v>76358.97</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.56</v>
+        <v>24.57</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1001,11 +1005,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>14.27</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1048,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4647.97</v>
+        <v>7471.93</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>59875.68</v>
+        <v>57051.72</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7.2</v>
+        <v>11.58</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1063,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2610.41</v>
+        <v>1162.28</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1110,22 +1114,26 @@
         <v>120920.56</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>120920.56</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>120920.56</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
       <c r="M11" t="n">
-        <v>300771.79</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1168,13 +1176,13 @@
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>62.75</v>
+        <v>135.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42450</v>
+        <v>42376.85</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1183,11 +1191,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>73.15000000000001</v>
+        <v>34.22</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1230,13 +1238,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>228.79</v>
+        <v>448.37</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38252.35</v>
+        <v>38032.77</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.59</v>
+        <v>1.17</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1245,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>196.73</v>
+        <v>3.44</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1292,13 +1300,13 @@
         <v>31834.46</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>31498.23</v>
+        <v>31819.47</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>336.23</v>
+        <v>14.99</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>98.94</v>
+        <v>99.95</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1307,11 +1315,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>321.23</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1474,13 +1482,13 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>23.33</v>
+        <v>62.96</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5449.17</v>
+        <v>5409.54</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.43</v>
+        <v>1.15</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1489,11 +1497,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>39.15</v>
+        <v>0.76</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1594,13 +1602,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>602.73</v>
+        <v>925.78</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2929.18</v>
+        <v>2606.13</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17.07</v>
+        <v>26.21</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1609,11 +1617,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>307.04</v>
+        <v>188.04</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1882,13 +1890,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>14296.74</v>
+        <v>23550.07</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>65620.82000000001</v>
+        <v>56367.49</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17.89</v>
+        <v>29.47</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1897,11 +1905,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9253.32</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1944,10 +1952,10 @@
         <v>53152.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>19291.18</v>
+        <v>19291.53</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33861.4</v>
+        <v>33861.05</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>36.29</v>
@@ -1959,11 +1967,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2130,13 +2138,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8155.21</v>
+        <v>10065.46</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12516.65</v>
+        <v>10606.4</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39.45</v>
+        <v>48.69</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2145,11 +2153,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1662.21</v>
+        <v>981.39</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2192,13 +2200,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2556.6</v>
+        <v>3955.14</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5728.25</v>
+        <v>4329.71</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30.86</v>
+        <v>47.74</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2207,11 +2215,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1353.31</v>
+        <v>513.6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2254,22 +2262,26 @@
         <v>22682.31</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>10961.73</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22682.31</v>
+        <v>11720.58</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>48.33</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>15-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>10961.73</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2327,11 +2339,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>132.07</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2374,13 +2386,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>32.87</v>
+        <v>286.43</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7382.1</v>
+        <v>7128.54</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.44</v>
+        <v>3.86</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2389,11 +2401,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>173.23</v>
+        <v>88.52</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2451,7 +2463,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -2498,13 +2510,13 @@
         <v>5260.44</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>512.29</v>
+        <v>611.75</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4748.15</v>
+        <v>4648.69</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>9.74</v>
+        <v>11.63</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2513,11 +2525,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>99.45999999999999</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2662,13 +2674,13 @@
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2014.93</v>
+        <v>2035.85</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2981.03</v>
+        <v>2960.11</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>40.33</v>
+        <v>40.75</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2677,11 +2689,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>20.91</v>
+        <v>18.55</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2724,13 +2736,13 @@
         <v>8960.700000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8.93</v>
+        <v>9.43</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8951.77</v>
+        <v>8951.27</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2739,11 +2751,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2786,13 +2798,13 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1184.58</v>
+        <v>1682.58</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5320.2</v>
+        <v>4822.2</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18.21</v>
+        <v>25.87</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2801,11 +2813,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>460.33</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2848,13 +2860,13 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.43</v>
+        <v>163.85</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2320.42</v>
+        <v>2215</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.46</v>
+        <v>6.89</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2863,11 +2875,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>104.18</v>
+        <v>1.26</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2910,13 +2922,13 @@
         <v>5183.78</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>18.57</v>
+        <v>1594.02</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5165.2</v>
+        <v>3589.76</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.36</v>
+        <v>30.75</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2925,11 +2937,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1575.44</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3034,13 +3046,13 @@
         <v>3021.64</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>6.33</v>
+        <v>218.09</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3015.31</v>
+        <v>2803.55</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.21</v>
+        <v>7.22</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3049,11 +3061,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>211.76</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3154,13 +3166,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>364.18</v>
+        <v>437.87</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>208.14</v>
+        <v>134.45</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>63.63</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3169,11 +3181,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>56.02</v>
+        <v>2.65</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3216,13 +3228,13 @@
         <v>427.29</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>427.29</v>
+        <v>427.12</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3231,11 +3243,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3438,13 +3450,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5714.76</v>
+        <v>6214.6</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7531.46</v>
+        <v>7031.62</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>43.14</v>
+        <v>46.92</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3453,11 +3465,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>489.33</v>
+        <v>41.17</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3500,13 +3512,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>134.4</v>
+        <v>291.39</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9973.34</v>
+        <v>9816.35</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.33</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3515,11 +3527,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>93.28</v>
+        <v>27.6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3562,13 +3574,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1582.93</v>
+        <v>5072.64</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23888.11</v>
+        <v>20398.4</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.21</v>
+        <v>19.92</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3577,11 +3589,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3489.71</v>
+        <v>165.86</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3624,13 +3636,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1688.43</v>
+        <v>2247.74</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15571.11</v>
+        <v>15011.8</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>13.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3639,11 +3651,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>536.54</v>
+        <v>42.26</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3686,13 +3698,13 @@
         <v>13151.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>291.74</v>
+        <v>578.46</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12859.9</v>
+        <v>12573.18</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.22</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3701,11 +3713,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>286.6</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3748,13 +3760,13 @@
         <v>10963.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>400.33</v>
+        <v>775.39</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10563</v>
+        <v>10187.94</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.65</v>
+        <v>7.07</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3763,11 +3775,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>375.06</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3810,13 +3822,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1077.51</v>
+        <v>1334.72</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8435.93</v>
+        <v>8178.72</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.33</v>
+        <v>14.03</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3825,11 +3837,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>238.69</v>
+        <v>303.48</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3930,13 +3942,13 @@
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3144.18</v>
+        <v>3593.97</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5298.39</v>
+        <v>4848.6</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>37.24</v>
+        <v>42.57</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3945,11 +3957,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>386.14</v>
+        <v>4843.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3992,13 +4004,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>148.93</v>
+        <v>320.46</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5405.32</v>
+        <v>5233.79</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.68</v>
+        <v>5.77</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4007,11 +4019,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>159.28</v>
+        <v>48.86</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4054,13 +4066,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>109.84</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>337.95</v>
+        <v>299.21</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17.38</v>
+        <v>26.85</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4069,11 +4081,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>35.6</v>
+        <v>13.42</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4131,7 +4143,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -4280,13 +4292,13 @@
         <v>928.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>34.24</v>
+        <v>40.24</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>894.25</v>
+        <v>888.25</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.69</v>
+        <v>4.33</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4295,11 +4307,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4342,13 +4354,13 @@
         <v>1497.03</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>209.97</v>
+        <v>250.21</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1287.06</v>
+        <v>1246.83</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14.03</v>
+        <v>16.71</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4357,11 +4369,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>25.41</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4578,13 +4590,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>32.12</v>
+        <v>35.4</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>239.26</v>
+        <v>235.98</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11.84</v>
+        <v>13.05</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4593,11 +4605,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3.28</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4800,13 +4812,13 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>93.55</v>
+        <v>116.74</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>432.48</v>
+        <v>409.29</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17.78</v>
+        <v>22.19</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4815,11 +4827,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>23.19</v>
+        <v>20.86</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4943,7 +4955,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>11.27</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5001,7 +5013,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5382,13 +5394,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4694</v>
+        <v>23824.4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>62799.58</v>
+        <v>43669.18</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6.95</v>
+        <v>35.3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5397,11 +5409,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>17500.06</v>
+        <v>9252.27</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5444,13 +5456,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>12472.72</v>
+        <v>16179.72</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>51179.95</v>
+        <v>47472.95</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.59</v>
+        <v>25.42</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5459,11 +5471,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3706.66</v>
+        <v>2.05</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5506,13 +5518,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>29835.65</v>
+        <v>30848.4</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>30317.26</v>
+        <v>29304.51</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49.6</v>
+        <v>51.28</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5521,11 +5533,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>981.25</v>
+        <v>390.91</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5568,13 +5580,13 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>246.9</v>
+        <v>273.55</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19587.73</v>
+        <v>19561.08</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -5583,11 +5595,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>26.51</v>
+        <v>0.19</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5630,13 +5642,13 @@
         <v>29457.81</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.09</v>
+        <v>16.56</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29457.72</v>
+        <v>29441.25</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -5645,11 +5657,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>16.48</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5692,13 +5704,13 @@
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>890.51</v>
+        <v>1049.44</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25658.97</v>
+        <v>25500.04</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5707,11 +5719,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>158.93</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5827,11 +5839,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1243.43</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5874,26 +5886,26 @@
         <v>21283.6</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>14770.67</v>
+        <v>19331.27</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6512.93</v>
+        <v>1952.33</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>90.83</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>4560.6</v>
+        <v>5473.89</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -5936,13 +5948,13 @@
         <v>1294.54</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1081.77</v>
+        <v>1105.92</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>212.77</v>
+        <v>188.62</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>83.56</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -5951,11 +5963,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>24.15</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -5998,13 +6010,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>169.69</v>
+        <v>341.17</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>575.97</v>
+        <v>404.48</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22.76</v>
+        <v>45.75</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6013,11 +6025,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>147.2</v>
+        <v>83.33</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6060,13 +6072,13 @@
         <v>3533.82</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>51.18</v>
+        <v>52.64</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3482.64</v>
+        <v>3481.18</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -6075,11 +6087,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -6514,22 +6526,26 @@
         <v>7.27</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7.27</v>
+        <v>7.23</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>0.04</v>
+        <v>4.55</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -6856,13 +6872,13 @@
         <v>15495.38</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>932.75</v>
+        <v>3424.47</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14562.63</v>
+        <v>12070.91</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.02</v>
+        <v>22.1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6871,11 +6887,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2491.72</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7376,13 +7392,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7589.94</v>
+        <v>9368.73</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18529.99</v>
+        <v>16751.2</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>29.06</v>
+        <v>35.87</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7391,11 +7407,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1778.8</v>
+        <v>20.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7438,13 +7454,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>13786.28</v>
+        <v>22509.24</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>103710.64</v>
+        <v>94987.67999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11.73</v>
+        <v>19.16</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7453,11 +7469,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>8191.15</v>
+        <v>1063.61</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7624,13 +7640,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>19513.67</v>
+        <v>30834.67</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>38782.18</v>
+        <v>27461.18</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>33.47</v>
+        <v>52.89</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7639,11 +7655,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7004.27</v>
+        <v>4822.03</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7686,22 +7702,26 @@
         <v>38881.49</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>35497.87</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>38881.49</v>
+        <v>3383.62</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>35495.24</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7744,13 +7764,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1366.51</v>
+        <v>3308.25</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10233.57</v>
+        <v>8291.83</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.78</v>
+        <v>28.52</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7759,11 +7779,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1850.71</v>
+        <v>784.61</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8007,11 +8027,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>33.24</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -8156,13 +8176,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26270.83</v>
+        <v>34199.08</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>84428.03</v>
+        <v>76499.78</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>23.73</v>
+        <v>30.89</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8171,11 +8191,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7928.26</v>
+        <v>202.41</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8233,7 +8253,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -8280,13 +8300,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>679.29</v>
+        <v>1149.7</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33623.04</v>
+        <v>33152.63</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.98</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8295,11 +8315,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>468.01</v>
+        <v>119.99</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8404,13 +8424,13 @@
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>16393.26</v>
+        <v>20703.95</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9117.65</v>
+        <v>4806.96</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>64.26000000000001</v>
+        <v>81.16</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8419,11 +8439,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4310.69</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8466,22 +8486,26 @@
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>1853.32</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19514.4</v>
+        <v>17661.08</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>15-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>2097.23</v>
+        <v>2036.64</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8524,26 +8548,26 @@
         <v>23174.68</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20329.54</v>
+        <v>20986.55</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2845.14</v>
+        <v>2188.13</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>87.72</v>
+        <v>90.56</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>657.01</v>
+        <v>2276.73</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8586,13 +8610,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10716.92</v>
+        <v>10993.19</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11868.25</v>
+        <v>11591.98</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>47.45</v>
+        <v>48.67</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8601,11 +8625,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>178.07</v>
+        <v>47.08</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8648,13 +8672,13 @@
         <v>1878.7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>27.51</v>
+        <v>33.67</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1851.19</v>
+        <v>1845.03</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -8663,11 +8687,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>6.16</v>
+        <v>11.88</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8710,13 +8734,13 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>231.05</v>
+        <v>259.7</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>83.43000000000001</v>
+        <v>54.78</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>73.47</v>
+        <v>82.58</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8725,11 +8749,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>28.23</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8936,13 +8960,13 @@
         <v>41828.13</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>41627.58</v>
+        <v>41828.13</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>200.55</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>99.52</v>
+        <v>100</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -8951,11 +8975,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>677.11</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -8998,13 +9022,13 @@
         <v>12605.9</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2666.1</v>
+        <v>2672.2</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9939.799999999999</v>
+        <v>9933.700000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21.15</v>
+        <v>21.2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9013,11 +9037,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9184,13 +9208,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1288.48</v>
+        <v>1769.82</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6706.66</v>
+        <v>6225.32</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16.12</v>
+        <v>22.14</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9199,11 +9223,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>480.41</v>
+        <v>175.88</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9246,22 +9270,26 @@
         <v>12575.71</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>10364.09</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>12575.71</v>
+        <v>2211.62</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>82.41</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>10056.14</v>
+        <v>68.37</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9304,13 +9332,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5124</v>
+        <v>5423.44</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1844.09</v>
+        <v>1544.65</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>73.54000000000001</v>
+        <v>77.83</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9319,11 +9347,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>293.7</v>
+        <v>317.85</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9366,13 +9394,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>36.35</v>
+        <v>63.77</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1901.32</v>
+        <v>1873.9</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.88</v>
+        <v>3.29</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9381,11 +9409,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>5.17</v>
+        <v>1.16</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9592,13 +9620,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7635.43</v>
+        <v>8419.540000000001</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>30716.77</v>
+        <v>29932.66</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19.91</v>
+        <v>21.95</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9607,11 +9635,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>599.01</v>
+        <v>1032.57</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9654,13 +9682,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>884.6799999999999</v>
+        <v>1432.67</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14326.38</v>
+        <v>13778.39</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5.82</v>
+        <v>9.42</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9669,11 +9697,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>320.46</v>
+        <v>114.91</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9716,13 +9744,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1062.62</v>
+        <v>1733.44</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14555.4</v>
+        <v>13884.58</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.8</v>
+        <v>11.1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9731,11 +9759,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>622.26</v>
+        <v>259.95</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9778,13 +9806,13 @@
         <v>14278.53</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1025.09</v>
+        <v>3615.11</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>13253.44</v>
+        <v>10663.42</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.18</v>
+        <v>25.32</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -9793,11 +9821,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2590.02</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -9902,22 +9930,26 @@
         <v>11752.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>4979.22</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11752.33</v>
+        <v>6773.11</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>42.37</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>15-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>4979.22</v>
+        <v>436.57</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -10080,13 +10112,13 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1406.57</v>
+        <v>1449.11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4571.17</v>
+        <v>4528.63</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23.53</v>
+        <v>24.24</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -10095,11 +10127,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>15-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>42.54</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2514.16</v>
+        <v>3681.47</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>118368.19</v>
+        <v>117200.88</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>964.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>40236.23</v>
+        <v>40242.16</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>75221.28999999999</v>
+        <v>75215.36</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>34.85</v>
@@ -881,11 +881,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5.92</v>
+        <v>1971.02</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         <v>103743.08</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>90026.64</v>
+        <v>90082.78999999999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13716.44</v>
+        <v>13660.29</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>86.78</v>
+        <v>86.83</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -943,11 +943,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>56.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>7471.93</v>
+        <v>7576.63</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>57051.72</v>
+        <v>56947.02</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>11.58</v>
+        <v>11.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1162.28</v>
+        <v>3216.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1176,13 +1176,13 @@
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>135.9</v>
+        <v>170.12</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42376.85</v>
+        <v>42342.63</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1191,11 +1191,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>34.22</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>448.37</v>
+        <v>450.37</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38032.77</v>
+        <v>38030.77</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.17</v>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3.44</v>
+        <v>77.83</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1482,13 +1482,13 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62.96</v>
+        <v>63.57</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5409.54</v>
+        <v>5408.93</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1497,11 +1497,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.76</v>
+        <v>0.14</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1602,13 +1602,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>925.78</v>
+        <v>1091.2</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2606.13</v>
+        <v>2440.7</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26.21</v>
+        <v>30.9</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1617,11 +1617,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>188.04</v>
+        <v>101.57</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>7039.56</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2138,13 +2138,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10065.46</v>
+        <v>11069.56</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10606.4</v>
+        <v>9602.299999999999</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>48.69</v>
+        <v>53.55</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2153,11 +2153,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>981.39</v>
+        <v>432.06</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2200,13 +2200,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3955.14</v>
+        <v>4243.24</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4329.71</v>
+        <v>4041.61</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>47.74</v>
+        <v>51.22</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2215,11 +2215,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>513.6</v>
+        <v>856.26</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2386,13 +2386,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>286.43</v>
+        <v>382.74</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7128.54</v>
+        <v>7032.23</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.86</v>
+        <v>5.16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2401,11 +2401,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>88.52</v>
+        <v>202.05</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2798,13 +2798,13 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1682.58</v>
+        <v>1730.05</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4822.2</v>
+        <v>4774.73</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>25.87</v>
+        <v>26.6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2813,11 +2813,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>68.45999999999999</v>
+        <v>20.98</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2860,13 +2860,13 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>163.85</v>
+        <v>165.11</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2215</v>
+        <v>2213.74</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6.89</v>
+        <v>6.94</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2875,11 +2875,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3166,13 +3166,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>437.87</v>
+        <v>438.59</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>134.45</v>
+        <v>133.73</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>76.51000000000001</v>
+        <v>76.63</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3181,11 +3181,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6214.6</v>
+        <v>6237.11</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7031.62</v>
+        <v>7009.11</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46.92</v>
+        <v>47.09</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3465,11 +3465,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>41.17</v>
+        <v>28.65</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>291.39</v>
+        <v>318.99</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9816.35</v>
+        <v>9788.75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3527,11 +3527,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>27.6</v>
+        <v>20.37</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3574,13 +3574,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5072.64</v>
+        <v>5238.25</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20398.4</v>
+        <v>20232.79</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.92</v>
+        <v>20.57</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3589,11 +3589,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>165.86</v>
+        <v>190.96</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3636,13 +3636,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2247.74</v>
+        <v>2290</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15011.8</v>
+        <v>14969.54</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.02</v>
+        <v>13.27</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3651,11 +3651,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>42.26</v>
+        <v>619.95</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
         <v>10963.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>775.39</v>
+        <v>848.86</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10187.94</v>
+        <v>10114.47</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.07</v>
+        <v>7.74</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3775,11 +3775,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>120.65</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3822,13 +3822,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1334.72</v>
+        <v>1638.21</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8178.72</v>
+        <v>7875.23</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14.03</v>
+        <v>17.22</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3837,11 +3837,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>303.48</v>
+        <v>45.11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3942,26 +3942,26 @@
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3593.97</v>
+        <v>8392.34</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4848.6</v>
+        <v>50.23</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>42.57</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4843.5</v>
+        <v>110.27</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4004,13 +4004,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>320.46</v>
+        <v>369.21</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5233.79</v>
+        <v>5185.04</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.77</v>
+        <v>6.65</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>48.86</v>
+        <v>1.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4066,13 +4066,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>109.84</v>
+        <v>110.69</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>299.21</v>
+        <v>298.36</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>26.85</v>
+        <v>27.06</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4081,11 +4081,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>13.42</v>
+        <v>15.69</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4354,13 +4354,13 @@
         <v>1497.03</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>250.21</v>
+        <v>275.62</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1246.83</v>
+        <v>1221.41</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16.71</v>
+        <v>18.41</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4369,11 +4369,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>25.41</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4590,13 +4590,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>35.4</v>
+        <v>35.77</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>235.98</v>
+        <v>235.62</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.05</v>
+        <v>13.18</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>0.78</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4812,13 +4812,13 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>116.74</v>
+        <v>137.6</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>409.29</v>
+        <v>388.43</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22.19</v>
+        <v>26.16</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4827,11 +4827,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>20.86</v>
+        <v>34.95</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4936,13 +4936,13 @@
         <v>243.93</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>43.97</v>
+        <v>55.25</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>199.96</v>
+        <v>188.68</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18.03</v>
+        <v>22.65</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4951,11 +4951,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>11.27</v>
+        <v>14.27</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>12.56</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5394,13 +5394,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>23824.4</v>
+        <v>33039.1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>43669.18</v>
+        <v>34454.48</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35.3</v>
+        <v>48.95</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5409,11 +5409,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9252.27</v>
+        <v>47.87</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5456,10 +5456,10 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>16179.72</v>
+        <v>16181.77</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>47472.95</v>
+        <v>47470.9</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>25.42</v>
@@ -5471,11 +5471,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2.05</v>
+        <v>4859.42</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5518,13 +5518,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>30848.4</v>
+        <v>31078.37</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29304.51</v>
+        <v>29074.54</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.28</v>
+        <v>51.67</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5533,11 +5533,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>390.91</v>
+        <v>256.03</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5580,10 +5580,10 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>273.55</v>
+        <v>273.74</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19561.08</v>
+        <v>19560.89</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.38</v>
@@ -5595,11 +5595,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5704,13 +5704,13 @@
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1049.44</v>
+        <v>1360.64</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25500.04</v>
+        <v>25188.83</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.95</v>
+        <v>5.12</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -5886,13 +5886,13 @@
         <v>21283.6</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>19331.27</v>
+        <v>21283.6</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1952.33</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>90.83</v>
+        <v>100</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -5901,11 +5901,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>5473.89</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -6010,13 +6010,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>341.17</v>
+        <v>398.63</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>404.48</v>
+        <v>347.02</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>45.75</v>
+        <v>53.46</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6025,11 +6025,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>83.33</v>
+        <v>25.96</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1023.07</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7392,13 +7392,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9368.73</v>
+        <v>9461.4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16751.2</v>
+        <v>16658.53</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35.87</v>
+        <v>36.22</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7407,11 +7407,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>20.7</v>
+        <v>1937.96</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7454,13 +7454,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>22509.24</v>
+        <v>22537.39</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>94987.67999999999</v>
+        <v>94959.53</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.16</v>
+        <v>19.18</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7469,11 +7469,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1063.61</v>
+        <v>2102.15</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7640,13 +7640,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>30834.67</v>
+        <v>35656.71</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27461.18</v>
+        <v>22639.14</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>52.89</v>
+        <v>61.17</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7655,11 +7655,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4822.03</v>
+        <v>517.25</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7764,13 +7764,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3308.25</v>
+        <v>3705.24</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8291.83</v>
+        <v>7894.84</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>28.52</v>
+        <v>31.94</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7779,11 +7779,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>784.61</v>
+        <v>803.8099999999999</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>202.41</v>
+        <v>4232.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8300,13 +8300,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1149.7</v>
+        <v>1174.92</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33152.63</v>
+        <v>33127.41</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8315,11 +8315,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>119.99</v>
+        <v>251.88</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8486,13 +8486,13 @@
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1853.32</v>
+        <v>3918.05</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>17661.08</v>
+        <v>15596.35</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.5</v>
+        <v>20.08</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -8501,11 +8501,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2036.64</v>
+        <v>2.55</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8548,13 +8548,13 @@
         <v>23174.68</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20986.55</v>
+        <v>23174.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2188.13</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>90.56</v>
+        <v>100</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8563,11 +8563,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2276.73</v>
+        <v>25.42</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10993.19</v>
+        <v>11040.27</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11591.98</v>
+        <v>11544.9</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48.67</v>
+        <v>48.88</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8625,11 +8625,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>47.08</v>
+        <v>103.22</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8672,13 +8672,13 @@
         <v>1878.7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>33.67</v>
+        <v>45.55</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1845.03</v>
+        <v>1833.15</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.79</v>
+        <v>2.42</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -8687,11 +8687,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>11.88</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -9208,13 +9208,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1769.82</v>
+        <v>1837.29</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6225.32</v>
+        <v>6157.85</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22.14</v>
+        <v>22.98</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9223,11 +9223,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>175.88</v>
+        <v>355.23</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9270,13 +9270,13 @@
         <v>12575.71</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10364.09</v>
+        <v>10548.07</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2211.62</v>
+        <v>2027.64</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>82.41</v>
+        <v>83.88</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -9285,11 +9285,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>68.37</v>
+        <v>938.66</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9332,13 +9332,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5423.44</v>
+        <v>5741.29</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1544.65</v>
+        <v>1226.8</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>77.83</v>
+        <v>82.39</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9347,11 +9347,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>317.85</v>
+        <v>181.22</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9394,13 +9394,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.77</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1873.9</v>
+        <v>1872.74</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9409,11 +9409,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9620,13 +9620,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8419.540000000001</v>
+        <v>9452.110000000001</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29932.66</v>
+        <v>28900.09</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21.95</v>
+        <v>24.65</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9635,11 +9635,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1032.57</v>
+        <v>402.29</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9682,13 +9682,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1432.67</v>
+        <v>1547.59</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13778.39</v>
+        <v>13663.47</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.42</v>
+        <v>10.17</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9697,11 +9697,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>114.91</v>
+        <v>194.38</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9744,13 +9744,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1733.44</v>
+        <v>1933.06</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13884.58</v>
+        <v>13684.96</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11.1</v>
+        <v>12.38</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9759,11 +9759,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>259.95</v>
+        <v>259.29</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9930,13 +9930,13 @@
         <v>11752.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4979.22</v>
+        <v>5415.79</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6773.11</v>
+        <v>6336.54</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>42.37</v>
+        <v>46.08</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9945,11 +9945,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>19-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>436.57</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>696.8200000000001</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,11 +571,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1513.03</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -618,10 +618,10 @@
         <v>137884.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.32</v>
+        <v>1.32</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>137884.46</v>
+        <v>137883.46</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -633,11 +633,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.99</v>
+        <v>1.54</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>266.66</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1971.02</v>
+        <v>6784.69</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>7576.63</v>
+        <v>8718.98</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>56947.02</v>
+        <v>55804.67</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>11.74</v>
+        <v>13.51</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3216.4</v>
+        <v>3195.26</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1129,11 +1129,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>19.16</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>450.37</v>
+        <v>481.88</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38030.77</v>
+        <v>37999.26</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>77.83</v>
+        <v>58.46</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.57</v>
+        <v>63.71</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5408.93</v>
+        <v>5408.79</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.16</v>
@@ -1497,11 +1497,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1602,13 +1602,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1091.2</v>
+        <v>1113.83</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2440.7</v>
+        <v>2418.09</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30.9</v>
+        <v>31.54</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1617,11 +1617,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>101.57</v>
+        <v>218.18</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>7039.56</v>
+        <v>22389.24</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>666.75</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2138,13 +2138,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>11069.56</v>
+        <v>11137.78</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9602.299999999999</v>
+        <v>9534.08</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>53.55</v>
+        <v>53.88</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2153,11 +2153,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>432.06</v>
+        <v>1056.58</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2200,13 +2200,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4243.24</v>
+        <v>4509.63</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4041.61</v>
+        <v>3775.22</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.22</v>
+        <v>54.43</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2215,11 +2215,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>856.26</v>
+        <v>779.27</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2262,13 +2262,13 @@
         <v>22682.31</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10961.73</v>
+        <v>11140.24</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11720.58</v>
+        <v>11542.07</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>48.33</v>
+        <v>49.11</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2386,13 +2386,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>382.74</v>
+        <v>423.96</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7032.23</v>
+        <v>6991.01</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5.16</v>
+        <v>5.72</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2401,11 +2401,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>202.05</v>
+        <v>452.33</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2510,13 +2510,13 @@
         <v>5260.44</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>611.75</v>
+        <v>914.54</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4648.69</v>
+        <v>4345.9</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>11.63</v>
+        <v>17.39</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -2674,13 +2674,13 @@
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2035.85</v>
+        <v>2054.4</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2960.11</v>
+        <v>2941.56</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>40.75</v>
+        <v>41.12</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2689,11 +2689,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18.55</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2798,13 +2798,13 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1730.05</v>
+        <v>1751.04</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4774.73</v>
+        <v>4753.74</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>26.6</v>
+        <v>26.92</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2813,11 +2813,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>20.98</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3166,13 +3166,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>438.59</v>
+        <v>440.74</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>133.73</v>
+        <v>131.58</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>76.63</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3181,11 +3181,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>32.92</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6237.11</v>
+        <v>6255.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7009.11</v>
+        <v>6990.45</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>47.09</v>
+        <v>47.23</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3465,11 +3465,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>28.65</v>
+        <v>312.44</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>318.99</v>
+        <v>338.99</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9788.75</v>
+        <v>9768.75</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3527,11 +3527,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>20.37</v>
+        <v>1.74</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3574,13 +3574,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5238.25</v>
+        <v>5284.85</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20232.79</v>
+        <v>20186.19</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20.57</v>
+        <v>20.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3589,11 +3589,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>190.96</v>
+        <v>689.95</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>619.95</v>
+        <v>657.89</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3837,11 +3837,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>45.11</v>
+        <v>126.92</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3942,13 +3942,13 @@
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8392.34</v>
+        <v>8442.57</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>50.23</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3957,11 +3957,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>110.27</v>
+        <v>41.99</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4004,13 +4004,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>369.21</v>
+        <v>369.86</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5185.04</v>
+        <v>5184.39</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.6</v>
+        <v>37.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4066,13 +4066,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>110.69</v>
+        <v>126.18</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>298.36</v>
+        <v>282.87</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>27.06</v>
+        <v>30.85</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4081,11 +4081,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>15.69</v>
+        <v>8.42</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4128,13 +4128,13 @@
         <v>31.27</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.55</v>
+        <v>31.27</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.72</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.76</v>
+        <v>100</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -4292,13 +4292,13 @@
         <v>928.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40.24</v>
+        <v>106.81</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>888.25</v>
+        <v>821.6799999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.33</v>
+        <v>11.5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>66.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4590,13 +4590,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>35.77</v>
+        <v>36.54</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>235.62</v>
+        <v>234.84</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.18</v>
+        <v>13.46</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4605,11 +4605,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.78</v>
+        <v>0.46</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4812,13 +4812,13 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>137.6</v>
+        <v>149.45</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>388.43</v>
+        <v>376.58</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>26.16</v>
+        <v>28.41</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4827,11 +4827,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>34.95</v>
+        <v>23.1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4936,13 +4936,13 @@
         <v>243.93</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>55.25</v>
+        <v>69.52</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>188.68</v>
+        <v>174.41</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22.65</v>
+        <v>28.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4951,11 +4951,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>14.27</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4998,22 +4998,26 @@
         <v>35.59</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>35.59</v>
+        <v>35.49</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>20-10-2026</t>
+        </is>
+      </c>
       <c r="M5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5114,22 +5118,26 @@
         <v>44.89</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>12.56</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>44.89</v>
+        <v>32.33</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>27.98</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>20-10-2026</t>
+        </is>
+      </c>
       <c r="M7" t="n">
-        <v>12.56</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5394,13 +5402,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>33039.1</v>
+        <v>33076.67</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34454.48</v>
+        <v>34416.91</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>48.95</v>
+        <v>49.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5409,11 +5417,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>47.87</v>
+        <v>38.07</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5456,13 +5464,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>16181.77</v>
+        <v>16202.79</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>47470.9</v>
+        <v>47449.88</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>25.42</v>
+        <v>25.46</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5471,11 +5479,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4859.42</v>
+        <v>6836.48</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5518,13 +5526,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>31078.37</v>
+        <v>31334.39</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29074.54</v>
+        <v>28818.52</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>51.67</v>
+        <v>52.09</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5533,11 +5541,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>256.03</v>
+        <v>230.43</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5599,7 +5607,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5723,7 +5731,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>117.07</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5905,7 +5913,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -6010,13 +6018,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>398.63</v>
+        <v>424.88</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>347.02</v>
+        <v>320.77</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>53.46</v>
+        <v>56.98</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6025,11 +6033,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>25.96</v>
+        <v>18.05</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6526,13 +6534,13 @@
         <v>7.27</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.04</v>
+        <v>4.59</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7.23</v>
+        <v>2.68</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.55</v>
+        <v>63.14</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -6541,11 +6549,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -6872,13 +6880,13 @@
         <v>15495.38</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3424.47</v>
+        <v>3446.16</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12070.91</v>
+        <v>12049.22</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22.1</v>
+        <v>22.24</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6887,11 +6895,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1023.07</v>
+        <v>1023.14</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7392,13 +7400,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9461.4</v>
+        <v>9483.07</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16658.53</v>
+        <v>16636.86</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>36.22</v>
+        <v>36.31</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7407,11 +7415,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1937.96</v>
+        <v>2793.32</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7454,13 +7462,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>22537.39</v>
+        <v>23572.85</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>94959.53</v>
+        <v>93924.07000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.18</v>
+        <v>20.06</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7469,11 +7477,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2102.15</v>
+        <v>3556.09</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7640,13 +7648,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>35656.71</v>
+        <v>36121.02</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22639.14</v>
+        <v>22174.83</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>61.17</v>
+        <v>61.96</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7655,11 +7663,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>517.25</v>
+        <v>233.84</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7721,7 +7729,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>317.06</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7764,13 +7772,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>3705.24</v>
+        <v>4129.19</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7894.84</v>
+        <v>7470.89</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>31.94</v>
+        <v>35.6</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7779,11 +7787,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>803.8099999999999</v>
+        <v>590.21</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8176,13 +8184,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>34199.08</v>
+        <v>34442.85</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>76499.78</v>
+        <v>76256.00999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>30.89</v>
+        <v>31.11</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8191,11 +8199,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4232.7</v>
+        <v>6134.98</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8253,7 +8261,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -8300,13 +8308,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1174.92</v>
+        <v>1319.4</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33127.41</v>
+        <v>32982.93</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.43</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8315,11 +8323,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>251.88</v>
+        <v>232.93</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8443,7 +8451,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8486,13 +8494,13 @@
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3918.05</v>
+        <v>3941.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15596.35</v>
+        <v>15572.85</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20.08</v>
+        <v>20.2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -8501,11 +8509,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.55</v>
+        <v>24.37</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8563,11 +8571,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>25.42</v>
+        <v>21</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8629,7 +8637,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>103.22</v>
+        <v>271.28</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8753,7 +8761,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9208,13 +9216,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1837.29</v>
+        <v>2070.26</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6157.85</v>
+        <v>5924.88</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22.98</v>
+        <v>25.89</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9223,11 +9231,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>355.23</v>
+        <v>301.07</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9270,13 +9278,13 @@
         <v>12575.71</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10548.07</v>
+        <v>11221.1</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2027.64</v>
+        <v>1354.61</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>83.88</v>
+        <v>89.23</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -9285,11 +9293,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>938.66</v>
+        <v>3328.36</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9332,13 +9340,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5741.29</v>
+        <v>5828.07</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1226.8</v>
+        <v>1140.02</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>82.39</v>
+        <v>83.64</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9347,11 +9355,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>181.22</v>
+        <v>444.96</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9394,13 +9402,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.93000000000001</v>
+        <v>66.38</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1872.74</v>
+        <v>1871.29</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9409,11 +9417,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.45</v>
+        <v>0.13</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9620,13 +9628,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9452.110000000001</v>
+        <v>9606.379999999999</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28900.09</v>
+        <v>28745.82</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>24.65</v>
+        <v>25.05</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9635,11 +9643,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>402.29</v>
+        <v>248.02</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9682,13 +9690,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1547.59</v>
+        <v>1581.16</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13663.47</v>
+        <v>13629.9</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10.17</v>
+        <v>10.39</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9697,11 +9705,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>194.38</v>
+        <v>340.16</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9744,13 +9752,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1933.06</v>
+        <v>2123.98</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13684.96</v>
+        <v>13494.04</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12.38</v>
+        <v>13.6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9759,11 +9767,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>20-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>259.29</v>
+        <v>662.37</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9887,7 +9895,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1112.79</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -10131,7 +10139,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>696.8200000000001</v>
+        <v>1042.99</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,11 +571,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1513.03</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -618,10 +618,10 @@
         <v>137884.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.32</v>
+        <v>2.85</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>137883.46</v>
+        <v>137881.93</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -633,11 +633,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3681.47</v>
+        <v>3948.13</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>117200.88</v>
+        <v>116934.22</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>266.66</v>
+        <v>140.47</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>40242.16</v>
+        <v>46908.9</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>75215.36</v>
+        <v>68548.62</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>34.85</v>
+        <v>40.63</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -881,11 +881,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>6784.69</v>
+        <v>1010.52</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8718.98</v>
+        <v>11131.82</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>55804.67</v>
+        <v>53391.83</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13.51</v>
+        <v>17.25</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3195.26</v>
+        <v>1455.89</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1129,11 +1129,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>765</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1176,13 +1176,13 @@
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>170.12</v>
+        <v>189.28</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42342.63</v>
+        <v>42323.47</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1191,11 +1191,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>19.16</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>481.88</v>
+        <v>528.3200000000001</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37999.26</v>
+        <v>37952.82</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>58.46</v>
+        <v>42.31</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1482,13 +1482,13 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.71</v>
+        <v>63.76</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5408.79</v>
+        <v>5408.74</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1497,11 +1497,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1602,13 +1602,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1113.83</v>
+        <v>1285.63</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2418.09</v>
+        <v>2246.28</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31.54</v>
+        <v>36.4</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1617,11 +1617,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>218.18</v>
+        <v>211.15</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1890,13 +1890,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>23550.07</v>
+        <v>45074.45</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>56367.49</v>
+        <v>34843.11</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>29.47</v>
+        <v>56.4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1905,11 +1905,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>22389.24</v>
+        <v>1604.15</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2138,13 +2138,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>11137.78</v>
+        <v>12100.33</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9534.08</v>
+        <v>8571.530000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>53.88</v>
+        <v>58.54</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2153,11 +2153,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1056.58</v>
+        <v>455.75</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2200,13 +2200,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4509.63</v>
+        <v>5122.65</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3775.22</v>
+        <v>3162.2</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>54.43</v>
+        <v>61.83</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2215,11 +2215,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>779.27</v>
+        <v>365.39</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2386,13 +2386,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>423.96</v>
+        <v>876.29</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6991.01</v>
+        <v>6538.68</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5.72</v>
+        <v>11.82</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2401,11 +2401,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>452.33</v>
+        <v>98.39</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>41.71</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2736,13 +2736,13 @@
         <v>8960.700000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.43</v>
+        <v>10.54</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8951.27</v>
+        <v>8950.16</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2751,11 +2751,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>180.96</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3166,13 +3166,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>440.74</v>
+        <v>441.11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>131.58</v>
+        <v>131.21</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>77.01000000000001</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3181,11 +3181,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2.96</v>
+        <v>32.97</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3228,13 +3228,13 @@
         <v>427.29</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.17</v>
+        <v>33.1</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>427.12</v>
+        <v>394.19</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.04</v>
+        <v>7.75</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3243,11 +3243,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>32.92</v>
+        <v>0.02</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3450,13 +3450,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6255.77</v>
+        <v>6482.68</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6990.45</v>
+        <v>6763.54</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>47.23</v>
+        <v>48.94</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3465,11 +3465,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>312.44</v>
+        <v>463.49</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>338.99</v>
+        <v>339.38</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9768.75</v>
+        <v>9768.360000000001</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3527,11 +3527,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1.74</v>
+        <v>33.38</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3574,13 +3574,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5284.85</v>
+        <v>5724.31</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20186.19</v>
+        <v>19746.73</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20.75</v>
+        <v>22.47</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3589,11 +3589,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>689.95</v>
+        <v>315.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3636,13 +3636,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2290</v>
+        <v>2947.89</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14969.54</v>
+        <v>14311.65</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.27</v>
+        <v>17.08</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3651,11 +3651,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>657.89</v>
+        <v>0.98</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
         <v>10963.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>848.86</v>
+        <v>969.51</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10114.47</v>
+        <v>9993.82</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.74</v>
+        <v>8.84</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3775,11 +3775,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>120.65</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3822,13 +3822,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1638.21</v>
+        <v>1725.51</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7875.23</v>
+        <v>7787.93</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>17.22</v>
+        <v>18.14</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3837,11 +3837,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>126.92</v>
+        <v>94.69</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3957,11 +3957,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>41.99</v>
+        <v>20.92</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4004,13 +4004,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>369.86</v>
+        <v>399.26</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5184.39</v>
+        <v>5154.99</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.66</v>
+        <v>7.19</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4019,11 +4019,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>37.6</v>
+        <v>24.27</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4066,13 +4066,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>126.18</v>
+        <v>134.6</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>282.87</v>
+        <v>274.45</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>30.85</v>
+        <v>32.91</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4081,11 +4081,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>8.42</v>
+        <v>20.2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4128,13 +4128,13 @@
         <v>31.27</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>31.27</v>
+        <v>0.55</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>30.72</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>100</v>
+        <v>1.77</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.46</v>
+        <v>1.56</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4812,13 +4812,13 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>149.45</v>
+        <v>172.55</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>376.58</v>
+        <v>353.48</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>28.41</v>
+        <v>32.8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4827,11 +4827,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5402,13 +5402,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>33076.67</v>
+        <v>33109.76</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34416.91</v>
+        <v>34383.82</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.01</v>
+        <v>49.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5417,11 +5417,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>38.07</v>
+        <v>18.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5464,13 +5464,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>16202.79</v>
+        <v>23033.38</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>47449.88</v>
+        <v>40619.29</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>25.46</v>
+        <v>36.19</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5479,11 +5479,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>6836.48</v>
+        <v>297.25</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5526,13 +5526,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>31334.39</v>
+        <v>31464.41</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28818.52</v>
+        <v>28688.5</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>52.09</v>
+        <v>52.31</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5541,11 +5541,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>230.43</v>
+        <v>131.28</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5588,10 +5588,10 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>273.74</v>
+        <v>273.76</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19560.89</v>
+        <v>19560.87</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.38</v>
@@ -5603,11 +5603,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.02</v>
+        <v>4.94</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5650,13 +5650,13 @@
         <v>29457.81</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>16.56</v>
+        <v>20.41</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29441.25</v>
+        <v>29437.4</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -5665,11 +5665,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5712,13 +5712,13 @@
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1360.64</v>
+        <v>1477.71</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25188.83</v>
+        <v>25071.76</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5.12</v>
+        <v>5.57</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5727,11 +5727,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>117.07</v>
+        <v>63.52</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5909,11 +5909,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>25.83</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -6018,13 +6018,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>424.88</v>
+        <v>442.93</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>320.77</v>
+        <v>302.72</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>56.98</v>
+        <v>59.4</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6033,11 +6033,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>18.05</v>
+        <v>20.56</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -6880,13 +6880,13 @@
         <v>15495.38</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3446.16</v>
+        <v>4469.31</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12049.22</v>
+        <v>11026.08</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22.24</v>
+        <v>28.84</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6895,11 +6895,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1023.14</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7400,13 +7400,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9483.07</v>
+        <v>12225.15</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16636.86</v>
+        <v>13894.78</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>36.31</v>
+        <v>46.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7415,11 +7415,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2793.32</v>
+        <v>114.44</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7462,13 +7462,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23572.85</v>
+        <v>25558.53</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>93924.07000000001</v>
+        <v>91938.39</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20.06</v>
+        <v>21.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7477,11 +7477,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3556.09</v>
+        <v>2662.03</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7648,13 +7648,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>36121.02</v>
+        <v>36354.86</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22174.83</v>
+        <v>21940.99</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>61.96</v>
+        <v>62.36</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7663,11 +7663,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>233.84</v>
+        <v>890.77</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7710,13 +7710,13 @@
         <v>38881.49</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>35497.87</v>
+        <v>35814.93</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3383.62</v>
+        <v>3066.56</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>91.3</v>
+        <v>92.11</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -7725,11 +7725,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>317.06</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7772,13 +7772,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4129.19</v>
+        <v>4602.97</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7470.89</v>
+        <v>6997.11</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>35.6</v>
+        <v>39.68</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7787,11 +7787,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>590.21</v>
+        <v>557.74</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>34442.85</v>
+        <v>38674.04</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>76256.00999999999</v>
+        <v>72024.82000000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>31.11</v>
+        <v>34.94</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8199,11 +8199,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>6134.98</v>
+        <v>1903.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8308,13 +8308,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1319.4</v>
+        <v>1459.59</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32982.93</v>
+        <v>32842.74</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.85</v>
+        <v>4.26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8323,11 +8323,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>232.93</v>
+        <v>118.23</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.1</v>
+        <v>9.59</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8494,13 +8494,13 @@
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3941.55</v>
+        <v>4209.83</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15572.85</v>
+        <v>15304.57</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20.2</v>
+        <v>21.57</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -8509,11 +8509,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>24.37</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8571,11 +8571,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8618,13 +8618,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11040.27</v>
+        <v>11240.52</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11544.9</v>
+        <v>11344.65</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48.88</v>
+        <v>49.77</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8633,11 +8633,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>271.28</v>
+        <v>105.68</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8742,10 +8742,10 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>259.7</v>
+        <v>259.71</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>54.78</v>
+        <v>54.77</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>82.58</v>
@@ -8757,11 +8757,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>8.890000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9216,13 +9216,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2070.26</v>
+        <v>2348.2</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5924.88</v>
+        <v>5646.94</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25.89</v>
+        <v>29.37</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9231,11 +9231,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>301.07</v>
+        <v>107.01</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9278,13 +9278,13 @@
         <v>12575.71</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>11221.1</v>
+        <v>12575.71</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1354.61</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>89.23</v>
+        <v>100</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -9293,11 +9293,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3328.36</v>
+        <v>519.86</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9340,13 +9340,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5828.07</v>
+        <v>6250.82</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1140.02</v>
+        <v>717.27</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>83.64</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9355,11 +9355,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>444.96</v>
+        <v>293.37</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9402,10 +9402,10 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.38</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1871.29</v>
+        <v>1871.16</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>3.43</v>
@@ -9417,11 +9417,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.13</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9628,13 +9628,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9606.379999999999</v>
+        <v>9854.4</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28745.82</v>
+        <v>28497.8</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>25.05</v>
+        <v>25.69</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9643,11 +9643,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>248.02</v>
+        <v>60.21</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9690,13 +9690,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1581.16</v>
+        <v>1921.32</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13629.9</v>
+        <v>13289.74</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10.39</v>
+        <v>12.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9705,11 +9705,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>340.16</v>
+        <v>145.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9752,13 +9752,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2123.98</v>
+        <v>2299.64</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13494.04</v>
+        <v>13318.38</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13.6</v>
+        <v>14.72</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9767,11 +9767,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>662.37</v>
+        <v>615.25</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4000.38</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -10120,13 +10120,13 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1449.11</v>
+        <v>2487.21</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4528.63</v>
+        <v>3490.53</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>24.24</v>
+        <v>41.61</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -10135,11 +10135,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>21-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1042.99</v>
+        <v>4.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1.6</v>
+        <v>4.88</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>69730.64</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9657.84</v>
+        <v>9658.700000000001</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>60072.8</v>
+        <v>60071.94</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>13.85</v>
@@ -757,11 +757,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.86</v>
+        <v>2.07</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3948.13</v>
+        <v>4076.29</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>116934.22</v>
+        <v>116806.06</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.27</v>
+        <v>3.37</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>140.47</v>
+        <v>36.01</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46908.9</v>
+        <v>46779.65</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>68548.62</v>
+        <v>68677.87</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>40.63</v>
+        <v>40.52</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -881,11 +881,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1010.52</v>
+        <v>892.59</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2681.83</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11131.82</v>
+        <v>12567.95</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>53391.83</v>
+        <v>51955.7</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17.25</v>
+        <v>19.48</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1455.89</v>
+        <v>873.4400000000001</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>528.3200000000001</v>
+        <v>566.64</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37952.82</v>
+        <v>37914.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>42.31</v>
+        <v>73.98</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1544,22 +1544,26 @@
         <v>2377.67</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
+        <v>7.71</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2377.67</v>
+        <v>2369.96</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>22-10-2026</t>
+        </is>
+      </c>
       <c r="M18" t="n">
-        <v>7.71</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1602,13 +1606,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1285.63</v>
+        <v>1410.03</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2246.28</v>
+        <v>2121.88</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>36.4</v>
+        <v>39.92</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1617,11 +1621,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>211.15</v>
+        <v>207.88</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1890,13 +1894,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45074.45</v>
+        <v>44490.45</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>34843.11</v>
+        <v>35427.11</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>56.4</v>
+        <v>55.67</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1905,11 +1909,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1604.15</v>
+        <v>672.88</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1952,13 +1956,13 @@
         <v>53152.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>19291.53</v>
+        <v>19958.28</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33861.05</v>
+        <v>33194.3</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>36.29</v>
+        <v>37.55</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1967,11 +1971,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>666.75</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2138,13 +2142,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>12100.33</v>
+        <v>12447.03</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8571.530000000001</v>
+        <v>8224.83</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>58.54</v>
+        <v>60.21</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2153,11 +2157,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>455.75</v>
+        <v>466.94</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2200,13 +2204,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5122.65</v>
+        <v>5289.05</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3162.2</v>
+        <v>2995.8</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>61.83</v>
+        <v>63.84</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2215,11 +2219,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>365.39</v>
+        <v>461.62</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2386,13 +2390,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>876.29</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6538.68</v>
+        <v>6449.9</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>11.82</v>
+        <v>13.02</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2401,11 +2405,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>98.39</v>
+        <v>437.94</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2755,7 +2759,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2817,7 +2821,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>180.96</v>
+        <v>181.31</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2879,7 +2883,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>21.13</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3166,13 +3170,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>441.11</v>
+        <v>471.46</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>131.21</v>
+        <v>100.86</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>77.06999999999999</v>
+        <v>82.38</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3181,11 +3185,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>32.97</v>
+        <v>4.77</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3243,7 +3247,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -3450,13 +3454,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6482.68</v>
+        <v>6601.16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6763.54</v>
+        <v>6645.06</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>48.94</v>
+        <v>49.83</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3465,11 +3469,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>463.49</v>
+        <v>642.89</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3512,13 +3516,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>339.38</v>
+        <v>366.28</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9768.360000000001</v>
+        <v>9741.459999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3527,11 +3531,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>33.38</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3574,13 +3578,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>5724.31</v>
+        <v>6030.73</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19746.73</v>
+        <v>19440.31</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22.47</v>
+        <v>23.68</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3589,11 +3593,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>315.1</v>
+        <v>259.02</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3636,13 +3640,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2947.89</v>
+        <v>2948.88</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14311.65</v>
+        <v>14310.66</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17.08</v>
+        <v>17.09</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3651,11 +3655,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.98</v>
+        <v>21.62</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3717,7 +3721,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>26.52</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3822,13 +3826,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1725.51</v>
+        <v>1797.34</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7787.93</v>
+        <v>7716.1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.14</v>
+        <v>18.89</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3837,11 +3841,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>94.69</v>
+        <v>58.59</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3957,11 +3961,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>20.92</v>
+        <v>1.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4004,13 +4008,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>399.26</v>
+        <v>418.85</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5154.99</v>
+        <v>5135.4</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.19</v>
+        <v>7.54</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4019,11 +4023,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>24.27</v>
+        <v>150.65</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4081,11 +4085,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>20.2</v>
+        <v>31.91</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4311,7 +4315,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>6.71</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4373,7 +4377,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4590,13 +4594,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>36.54</v>
+        <v>37</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>234.84</v>
+        <v>234.38</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.46</v>
+        <v>13.64</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4605,11 +4609,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5340,10 +5344,10 @@
         <v>33586.54</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2.08</v>
+        <v>4.14</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33584.46</v>
+        <v>33582.4</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0.01</v>
@@ -5355,11 +5359,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5402,13 +5406,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>33109.76</v>
+        <v>33128.47</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34383.82</v>
+        <v>34365.11</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.06</v>
+        <v>49.08</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5417,11 +5421,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5464,13 +5468,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23033.38</v>
+        <v>23040.51</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40619.29</v>
+        <v>40612.16</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36.19</v>
+        <v>36.2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5479,11 +5483,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>297.25</v>
+        <v>722.52</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5526,13 +5530,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>31464.41</v>
+        <v>31595.69</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28688.5</v>
+        <v>28557.22</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>52.31</v>
+        <v>52.53</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5541,11 +5545,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>131.28</v>
+        <v>46.78</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5588,13 +5592,13 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>273.76</v>
+        <v>278.7</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19560.87</v>
+        <v>19555.93</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -5603,11 +5607,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4.94</v>
+        <v>1.69</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5669,7 +5673,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5712,13 +5716,13 @@
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1477.71</v>
+        <v>1541.23</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25071.76</v>
+        <v>25008.24</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5.57</v>
+        <v>5.81</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5727,11 +5731,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>63.52</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5956,13 +5960,13 @@
         <v>1294.54</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1105.92</v>
+        <v>1131.76</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>188.62</v>
+        <v>162.78</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>85.43000000000001</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -5971,11 +5975,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>25.83</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -6037,7 +6041,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>20.56</v>
+        <v>66.41</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6080,13 +6084,13 @@
         <v>3533.82</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>52.64</v>
+        <v>58.73</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3481.18</v>
+        <v>3475.09</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -6095,11 +6099,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>11</v>
+        <v>4.92</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -7400,13 +7404,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>12225.15</v>
+        <v>12278.88</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13894.78</v>
+        <v>13841.05</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46.8</v>
+        <v>47.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7415,11 +7419,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>114.44</v>
+        <v>74.23</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7462,13 +7466,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25558.53</v>
+        <v>27601.76</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>91938.39</v>
+        <v>89895.14999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21.75</v>
+        <v>23.49</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7477,11 +7481,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2662.03</v>
+        <v>626.6799999999999</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7648,13 +7652,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>36354.86</v>
+        <v>36595.19</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21940.99</v>
+        <v>21700.66</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62.36</v>
+        <v>62.77</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7663,11 +7667,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>890.77</v>
+        <v>1887.43</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7772,13 +7776,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4602.97</v>
+        <v>4846.34</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6997.11</v>
+        <v>6753.74</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39.68</v>
+        <v>41.78</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7787,11 +7791,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>557.74</v>
+        <v>700.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8184,13 +8188,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>38674.04</v>
+        <v>40577.83</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>72024.82000000001</v>
+        <v>70121.03</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>34.94</v>
+        <v>36.66</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8199,11 +8203,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1903.8</v>
+        <v>3.28</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8308,13 +8312,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1459.59</v>
+        <v>1575.85</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32842.74</v>
+        <v>32726.48</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.26</v>
+        <v>4.59</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8323,11 +8327,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>118.23</v>
+        <v>116.52</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8432,10 +8436,10 @@
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20703.95</v>
+        <v>20704.05</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4806.96</v>
+        <v>4806.86</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>81.16</v>
@@ -8447,11 +8451,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>9.59</v>
+        <v>32.36</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8513,7 +8517,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>30.57</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8618,13 +8622,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11240.52</v>
+        <v>11313.95</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11344.65</v>
+        <v>11271.22</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>49.77</v>
+        <v>50.09</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8633,11 +8637,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>105.68</v>
+        <v>140.97</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8699,7 +8703,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8742,13 +8746,13 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>259.71</v>
+        <v>268.59</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>54.77</v>
+        <v>45.89</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>82.58</v>
+        <v>85.41</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8757,11 +8761,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>8.880000000000001</v>
+        <v>21.27</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9216,13 +9220,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2348.2</v>
+        <v>2404.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5646.94</v>
+        <v>5590.46</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29.37</v>
+        <v>30.08</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9231,11 +9235,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>107.01</v>
+        <v>252.97</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9293,11 +9297,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>519.86</v>
+        <v>289.37</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9340,26 +9344,26 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6250.82</v>
+        <v>6503.22</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>717.27</v>
+        <v>464.87</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>89.70999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>293.37</v>
+        <v>752.87</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9402,13 +9406,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.51000000000001</v>
+        <v>70.11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1871.16</v>
+        <v>1867.56</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9417,11 +9421,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>0.35</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9483,7 +9487,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>48.02</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9628,13 +9632,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9854.4</v>
+        <v>9886.309999999999</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28497.8</v>
+        <v>28465.89</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>25.69</v>
+        <v>25.78</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9643,11 +9647,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>60.21</v>
+        <v>294.78</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9690,13 +9694,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1921.32</v>
+        <v>2036.35</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13289.74</v>
+        <v>13174.71</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12.63</v>
+        <v>13.39</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9705,11 +9709,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>145.2</v>
+        <v>187.63</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9752,13 +9756,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2299.64</v>
+        <v>2834.16</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13318.38</v>
+        <v>12783.86</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.72</v>
+        <v>18.15</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9767,11 +9771,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>615.25</v>
+        <v>158.83</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9876,13 +9880,13 @@
         <v>13880.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>848.36</v>
+        <v>1961.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13032.06</v>
+        <v>11919.27</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6.11</v>
+        <v>14.13</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -9891,11 +9895,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>08-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1112.79</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -10120,13 +10124,13 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2487.21</v>
+        <v>2492.11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3490.53</v>
+        <v>3485.63</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>41.61</v>
+        <v>41.69</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -10135,11 +10139,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>22-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4.9</v>
+        <v>609.3099999999999</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -618,13 +618,13 @@
         <v>137884.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.85</v>
+        <v>7.3</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>137881.93</v>
+        <v>137877.48</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>4.88</v>
+        <v>41.99</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>69730.64</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9658.700000000001</v>
+        <v>9659.57</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>60071.94</v>
+        <v>60071.07</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>13.85</v>
@@ -757,11 +757,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4076.29</v>
+        <v>4088.6</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>116806.06</v>
+        <v>116793.75</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>36.01</v>
+        <v>72.08</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46779.65</v>
+        <v>47672.24</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>68677.87</v>
+        <v>67785.28</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>40.52</v>
+        <v>41.29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -881,11 +881,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>892.59</v>
+        <v>137.05</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>12567.95</v>
+        <v>13420.65</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>51955.7</v>
+        <v>51103</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.48</v>
+        <v>20.8</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>873.4400000000001</v>
+        <v>989.53</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1176,10 +1176,10 @@
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>189.28</v>
+        <v>193.25</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42323.47</v>
+        <v>42319.5</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.45</v>
@@ -1191,11 +1191,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>566.64</v>
+        <v>581.1900000000001</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37914.5</v>
+        <v>37899.95</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>73.98</v>
+        <v>105.11</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1606,13 +1606,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1410.03</v>
+        <v>1569.76</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2121.88</v>
+        <v>1962.15</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>39.92</v>
+        <v>44.45</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1621,11 +1621,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>207.88</v>
+        <v>56.47</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>44490.45</v>
+        <v>45763.68</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>35427.11</v>
+        <v>34153.89</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>55.67</v>
+        <v>57.26</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>672.88</v>
+        <v>5017.09</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1956,13 +1956,13 @@
         <v>53152.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>19958.28</v>
+        <v>19357.93</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33194.3</v>
+        <v>33794.65</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>37.55</v>
+        <v>36.42</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>12447.03</v>
+        <v>12711.16</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>8224.83</v>
+        <v>7960.7</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>60.21</v>
+        <v>61.49</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>466.94</v>
+        <v>379.35</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2204,13 +2204,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5289.05</v>
+        <v>5488.89</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2995.8</v>
+        <v>2795.96</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>63.84</v>
+        <v>66.25</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>461.62</v>
+        <v>413.15</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>965.0700000000001</v>
+        <v>1377.48</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6449.9</v>
+        <v>6037.49</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13.02</v>
+        <v>18.58</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2405,11 +2405,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>437.94</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>214.59</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2054.4</v>
+        <v>2096.1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2941.56</v>
+        <v>2899.86</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>41.12</v>
+        <v>41.96</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2693,11 +2693,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>41.71</v>
+        <v>14.27</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2802,13 +2802,13 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1751.04</v>
+        <v>1931.99</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4753.74</v>
+        <v>4572.79</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>26.92</v>
+        <v>29.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2817,11 +2817,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>181.31</v>
+        <v>0.35</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3170,13 +3170,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>471.46</v>
+        <v>499.95</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>100.86</v>
+        <v>72.37</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>82.38</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3185,11 +3185,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4.77</v>
+        <v>1.55</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         <v>427.29</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>33.1</v>
+        <v>33.12</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>394.19</v>
+        <v>394.17</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>7.75</v>
@@ -3247,11 +3247,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3454,13 +3454,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6601.16</v>
+        <v>6969.23</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6645.06</v>
+        <v>6276.99</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>49.83</v>
+        <v>52.61</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3469,11 +3469,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>642.89</v>
+        <v>408.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3516,13 +3516,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>366.28</v>
+        <v>375.02</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9741.459999999999</v>
+        <v>9732.719999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3531,11 +3531,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>9.779999999999999</v>
+        <v>52.27</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6030.73</v>
+        <v>6129.68</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19440.31</v>
+        <v>19341.36</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23.68</v>
+        <v>24.07</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3593,11 +3593,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>259.02</v>
+        <v>296.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3640,13 +3640,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2948.88</v>
+        <v>2970.5</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14310.66</v>
+        <v>14289.04</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17.09</v>
+        <v>17.21</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3655,11 +3655,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>21.62</v>
+        <v>43.82</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3702,13 +3702,13 @@
         <v>13151.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>578.46</v>
+        <v>604.98</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12573.18</v>
+        <v>12546.66</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3717,11 +3717,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>26.52</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>114.72</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3826,13 +3826,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1797.34</v>
+        <v>1820.21</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7716.1</v>
+        <v>7693.23</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.89</v>
+        <v>19.13</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3841,11 +3841,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>58.59</v>
+        <v>54.34</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>418.85</v>
+        <v>493.63</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5135.4</v>
+        <v>5060.62</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.54</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4023,11 +4023,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>150.65</v>
+        <v>141.86</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4070,13 +4070,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>134.6</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>274.45</v>
+        <v>246.05</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>32.91</v>
+        <v>39.85</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4085,11 +4085,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>31.91</v>
+        <v>25.21</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         <v>928.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>106.81</v>
+        <v>113.52</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>821.6799999999999</v>
+        <v>814.97</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.5</v>
+        <v>12.23</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4311,11 +4311,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>9.279999999999999</v>
+        <v>2.57</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4594,13 +4594,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>37</v>
+        <v>38.1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>234.38</v>
+        <v>233.28</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.64</v>
+        <v>14.04</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4609,11 +4609,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>0.08</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -5184,22 +5184,26 @@
         <v>60.94</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>60.94</v>
+        <v>56.83</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>23-10-2026</t>
+        </is>
+      </c>
       <c r="M8" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5468,13 +5472,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23040.51</v>
+        <v>23351.14</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40612.16</v>
+        <v>40301.53</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36.2</v>
+        <v>36.69</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5483,11 +5487,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>722.52</v>
+        <v>2244.71</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5549,7 +5553,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>46.78</v>
+        <v>92.05</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5592,10 +5596,10 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>278.7</v>
+        <v>280.39</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19555.93</v>
+        <v>19554.24</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.41</v>
@@ -5607,11 +5611,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1.69</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5654,13 +5658,13 @@
         <v>29457.81</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>20.41</v>
+        <v>24.31</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29437.4</v>
+        <v>29433.5</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -5669,11 +5673,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -6022,13 +6026,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>442.93</v>
+        <v>467.86</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>302.72</v>
+        <v>277.79</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>59.4</v>
+        <v>62.75</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6037,11 +6041,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>66.41</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6084,13 +6088,13 @@
         <v>3533.82</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.73</v>
+        <v>63.65</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3475.09</v>
+        <v>3470.17</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -6099,11 +6103,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>4.92</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -6903,7 +6907,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7404,13 +7408,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>12278.88</v>
+        <v>12448.5</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13841.05</v>
+        <v>13671.43</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>47.01</v>
+        <v>47.66</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7419,11 +7423,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>74.23</v>
+        <v>915.04</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7466,13 +7470,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>27601.76</v>
+        <v>28228.44</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>89895.14999999999</v>
+        <v>89268.48</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23.49</v>
+        <v>24.02</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7481,11 +7485,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>626.6799999999999</v>
+        <v>8230.870000000001</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7652,13 +7656,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>36595.19</v>
+        <v>37450.86</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21700.66</v>
+        <v>20844.99</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62.77</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7667,11 +7671,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1887.43</v>
+        <v>1134.21</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7776,13 +7780,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4846.34</v>
+        <v>5202.82</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6753.74</v>
+        <v>6397.26</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>41.78</v>
+        <v>44.85</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7791,11 +7795,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>700.9</v>
+        <v>594.4299999999999</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8188,10 +8192,10 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40577.83</v>
+        <v>40581.11</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>70121.03</v>
+        <v>70117.75</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>36.66</v>
@@ -8203,11 +8207,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3.28</v>
+        <v>154.17</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8312,13 +8316,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1575.85</v>
+        <v>1617.98</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32726.48</v>
+        <v>32684.35</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8327,11 +8331,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>116.52</v>
+        <v>273.35</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8436,13 +8440,13 @@
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20704.05</v>
+        <v>20713.54</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4806.86</v>
+        <v>4797.37</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>81.16</v>
+        <v>81.19</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8451,11 +8455,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>32.36</v>
+        <v>22.86</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8498,13 +8502,13 @@
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4209.83</v>
+        <v>4230.58</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15304.57</v>
+        <v>15283.82</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.57</v>
+        <v>21.68</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -8513,11 +8517,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>30.57</v>
+        <v>42.06</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8622,13 +8626,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11313.95</v>
+        <v>11386.6</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11271.22</v>
+        <v>11198.57</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>50.09</v>
+        <v>50.42</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8637,11 +8641,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>140.97</v>
+        <v>175.68</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8684,13 +8688,13 @@
         <v>1878.7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45.55</v>
+        <v>46.9</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1833.15</v>
+        <v>1831.8</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -8699,11 +8703,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8746,26 +8750,26 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>268.59</v>
+        <v>289.86</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45.89</v>
+        <v>24.62</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>85.41</v>
+        <v>92.17</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>21.27</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9220,13 +9224,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2404.68</v>
+        <v>2523.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5590.46</v>
+        <v>5471.46</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30.08</v>
+        <v>31.57</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9235,11 +9239,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>252.97</v>
+        <v>318.59</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9344,13 +9348,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6503.22</v>
+        <v>6968.09</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>464.87</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9359,11 +9363,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>752.87</v>
+        <v>285.74</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9406,13 +9410,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>70.11</v>
+        <v>72.81</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1867.56</v>
+        <v>1864.86</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9421,11 +9425,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9468,13 +9472,13 @@
         <v>1831.54</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1747.44</v>
+        <v>1795.47</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>84.09</v>
+        <v>36.07</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>95.41</v>
+        <v>98.03</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -9483,11 +9487,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>48.02</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9632,13 +9636,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9886.309999999999</v>
+        <v>10135.03</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28465.89</v>
+        <v>28217.17</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>25.78</v>
+        <v>26.43</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9647,11 +9651,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>294.78</v>
+        <v>137.36</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9694,13 +9698,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2036.35</v>
+        <v>2223.97</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13174.71</v>
+        <v>12987.08</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.39</v>
+        <v>14.62</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9709,11 +9713,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>187.63</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9756,13 +9760,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2834.16</v>
+        <v>2948.5</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12783.86</v>
+        <v>12669.52</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18.15</v>
+        <v>18.88</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9771,11 +9775,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>158.83</v>
+        <v>159.8</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9818,13 +9822,13 @@
         <v>14278.53</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3615.11</v>
+        <v>7615.49</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10663.42</v>
+        <v>6663.04</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>25.32</v>
+        <v>53.34</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -9833,11 +9837,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>23-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4000.38</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -618,10 +618,10 @@
         <v>137884.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7.3</v>
+        <v>7.74</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>137877.48</v>
+        <v>137877.05</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0.01</v>
@@ -633,11 +633,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>41.99</v>
+        <v>55.55</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>69730.64</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9659.57</v>
+        <v>9660.77</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>60071.07</v>
+        <v>60069.87</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>13.85</v>
@@ -757,11 +757,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2.28</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4088.6</v>
+        <v>4136.46</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>116793.75</v>
+        <v>116745.89</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>72.08</v>
+        <v>72.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -990,13 +990,13 @@
         <v>101232.21</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>24873.24</v>
+        <v>27555.07</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>76358.97</v>
+        <v>73677.14</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.57</v>
+        <v>27.22</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1005,11 +1005,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>2681.83</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>13420.65</v>
+        <v>14410.18</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>51103</v>
+        <v>50113.47</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>20.8</v>
+        <v>22.33</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>989.53</v>
+        <v>905.08</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1129,11 +1129,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>581.1900000000001</v>
+        <v>681.0700000000001</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37899.95</v>
+        <v>37800.07</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>105.11</v>
+        <v>30.02</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.76</v>
+        <v>63.77</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5408.74</v>
+        <v>5408.73</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.17</v>
@@ -1497,11 +1497,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1606,13 +1606,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1569.76</v>
+        <v>1617.91</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1962.15</v>
+        <v>1914</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>44.45</v>
+        <v>45.81</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1621,11 +1621,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>56.47</v>
+        <v>55.76</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>12711.16</v>
+        <v>13052.32</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7960.7</v>
+        <v>7619.54</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>61.49</v>
+        <v>63.14</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>379.35</v>
+        <v>449.87</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2204,13 +2204,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5488.89</v>
+        <v>5760.83</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2795.96</v>
+        <v>2524.02</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>66.25</v>
+        <v>69.53</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>413.15</v>
+        <v>188.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1377.48</v>
+        <v>1446.2</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6037.49</v>
+        <v>5968.77</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18.58</v>
+        <v>19.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2405,11 +2405,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>71.31999999999999</v>
+        <v>141.09</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2514,13 +2514,13 @@
         <v>5260.44</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>914.54</v>
+        <v>1129.14</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4345.9</v>
+        <v>4131.3</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17.39</v>
+        <v>21.46</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2529,11 +2529,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>214.59</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         <v>4995.96</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2096.1</v>
+        <v>2110.37</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2899.86</v>
+        <v>2885.59</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>41.96</v>
+        <v>42.24</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2693,11 +2693,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>14.27</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         <v>8960.700000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.54</v>
+        <v>10.69</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8950.16</v>
+        <v>8950.01</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0.12</v>
@@ -2755,11 +2755,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2802,13 +2802,13 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1931.99</v>
+        <v>1932.35</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4572.79</v>
+        <v>4572.43</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29.7</v>
+        <v>29.71</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2817,11 +2817,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.35</v>
+        <v>756.26</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2864,13 +2864,13 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>165.11</v>
+        <v>186.24</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2213.74</v>
+        <v>2192.61</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6.94</v>
+        <v>7.83</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2879,11 +2879,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>21.13</v>
+        <v>0.58</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3170,13 +3170,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>499.95</v>
+        <v>507.71</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>72.37</v>
+        <v>64.61</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>87.34999999999999</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3185,11 +3185,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.55</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3454,13 +3454,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6969.23</v>
+        <v>7369.79</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6276.99</v>
+        <v>5876.43</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>52.61</v>
+        <v>55.64</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3469,11 +3469,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>408.8</v>
+        <v>537.92</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3516,13 +3516,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>375.02</v>
+        <v>381.36</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9732.719999999999</v>
+        <v>9726.379999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3531,11 +3531,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>52.27</v>
+        <v>68.06</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6129.68</v>
+        <v>6425.47</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19341.36</v>
+        <v>19045.57</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>24.07</v>
+        <v>25.23</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3593,11 +3593,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>296.1</v>
+        <v>365.42</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3640,13 +3640,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2970.5</v>
+        <v>3012.92</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14289.04</v>
+        <v>14246.62</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17.21</v>
+        <v>17.46</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3655,11 +3655,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>43.82</v>
+        <v>24.41</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>94.38</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>114.72</v>
+        <v>200.26</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3826,13 +3826,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1820.21</v>
+        <v>1874.55</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7693.23</v>
+        <v>7638.89</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19.13</v>
+        <v>19.7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3841,11 +3841,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>54.34</v>
+        <v>41.85</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>493.63</v>
+        <v>622.66</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5060.62</v>
+        <v>4931.59</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>11.21</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4023,11 +4023,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>141.86</v>
+        <v>44.47</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4070,13 +4070,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>163</v>
+        <v>167.94</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>246.05</v>
+        <v>241.11</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>39.85</v>
+        <v>41.06</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4085,11 +4085,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>25.21</v>
+        <v>24.84</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         <v>928.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>113.52</v>
+        <v>116.09</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>814.97</v>
+        <v>812.4</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12.23</v>
+        <v>12.5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4311,11 +4311,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4358,13 +4358,13 @@
         <v>1497.03</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>275.62</v>
+        <v>276.48</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1221.41</v>
+        <v>1220.55</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18.41</v>
+        <v>18.47</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4373,11 +4373,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.87</v>
+        <v>86.11</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.08</v>
+        <v>1.75</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4.7</v>
+        <v>35.95</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>14.64</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>61.32</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5472,13 +5472,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23351.14</v>
+        <v>24071.15</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40301.53</v>
+        <v>39581.52</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36.69</v>
+        <v>37.82</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5487,11 +5487,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2244.71</v>
+        <v>1912.82</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>31595.69</v>
+        <v>31692.3</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28557.22</v>
+        <v>28460.61</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>52.53</v>
+        <v>52.69</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5549,11 +5549,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>92.05</v>
+        <v>595.33</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5596,13 +5596,13 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>280.39</v>
+        <v>280.69</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19554.24</v>
+        <v>19553.94</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -5611,11 +5611,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>10.41</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>25.83</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -6026,13 +6026,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>467.86</v>
+        <v>518.77</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>277.79</v>
+        <v>226.88</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>62.75</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6041,11 +6041,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>67.65000000000001</v>
+        <v>24.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -7408,13 +7408,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>12448.5</v>
+        <v>12498.36</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13671.43</v>
+        <v>13621.57</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>47.66</v>
+        <v>47.85</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7423,11 +7423,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>915.04</v>
+        <v>871.73</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7470,13 +7470,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>28228.44</v>
+        <v>29233.08</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>89268.48</v>
+        <v>88263.84</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>24.02</v>
+        <v>24.88</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7485,11 +7485,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>8230.870000000001</v>
+        <v>8725.190000000001</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7656,13 +7656,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>37450.86</v>
+        <v>38482.62</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>20844.99</v>
+        <v>19813.23</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>64.23999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7671,11 +7671,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1134.21</v>
+        <v>384.04</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7780,13 +7780,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5202.82</v>
+        <v>5571.19</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6397.26</v>
+        <v>6028.89</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>44.85</v>
+        <v>48.03</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7795,11 +7795,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>594.4299999999999</v>
+        <v>502.72</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>154.17</v>
+        <v>172.59</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8316,13 +8316,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1617.98</v>
+        <v>1692.38</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32684.35</v>
+        <v>32609.95</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.72</v>
+        <v>4.93</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8331,11 +8331,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>273.35</v>
+        <v>277.75</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8440,13 +8440,13 @@
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20713.54</v>
+        <v>20736.41</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4797.37</v>
+        <v>4774.5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>81.19</v>
+        <v>81.28</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8455,11 +8455,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>22.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8502,13 +8502,13 @@
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4230.58</v>
+        <v>4256.51</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15283.82</v>
+        <v>15257.89</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.68</v>
+        <v>21.81</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -8517,11 +8517,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>42.06</v>
+        <v>42.08</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8626,13 +8626,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11386.6</v>
+        <v>11562.28</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11198.57</v>
+        <v>11022.89</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>50.42</v>
+        <v>51.19</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8641,11 +8641,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>175.68</v>
+        <v>1436.14</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8750,13 +8750,13 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>289.86</v>
+        <v>292.56</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.62</v>
+        <v>21.92</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>92.17</v>
+        <v>93.03</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8765,11 +8765,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9224,13 +9224,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2523.68</v>
+        <v>2722.37</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5471.46</v>
+        <v>5272.77</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31.57</v>
+        <v>34.05</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9239,11 +9239,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>318.59</v>
+        <v>269.33</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9301,11 +9301,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>289.37</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -9363,11 +9363,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>285.74</v>
+        <v>54.17</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9410,13 +9410,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>72.81</v>
+        <v>73.28</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1864.86</v>
+        <v>1864.39</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9425,11 +9425,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.47</v>
+        <v>1.39</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9636,13 +9636,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10135.03</v>
+        <v>10229.27</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28217.17</v>
+        <v>28122.93</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>26.43</v>
+        <v>26.67</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9651,11 +9651,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>137.36</v>
+        <v>43.12</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9698,13 +9698,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2223.97</v>
+        <v>2269.14</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12987.08</v>
+        <v>12941.92</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14.62</v>
+        <v>14.92</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9713,11 +9713,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>70.90000000000001</v>
+        <v>319.03</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9760,13 +9760,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2948.5</v>
+        <v>3061.89</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12669.52</v>
+        <v>12556.13</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18.88</v>
+        <v>19.6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9775,11 +9775,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>159.8</v>
+        <v>178.16</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -10128,13 +10128,13 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2492.11</v>
+        <v>3101.42</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3485.63</v>
+        <v>2876.32</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>41.69</v>
+        <v>51.88</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -10143,11 +10143,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>609.3099999999999</v>
+        <v>1781.65</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -618,13 +618,13 @@
         <v>137884.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7.74</v>
+        <v>49.29</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>137877.05</v>
+        <v>137835.49</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>55.55</v>
+        <v>14</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -742,13 +742,13 @@
         <v>69730.64</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9660.77</v>
+        <v>9661.85</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>60069.87</v>
+        <v>60068.79</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.85</v>
+        <v>13.86</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -757,11 +757,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>0.39</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4136.46</v>
+        <v>4184.78</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>116745.89</v>
+        <v>116697.57</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>72.8</v>
+        <v>92.97</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>47672.24</v>
+        <v>47809.29</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>67785.28</v>
+        <v>67648.23</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41.29</v>
+        <v>41.41</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -881,11 +881,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>137.05</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>14410.18</v>
+        <v>14467.15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>50113.47</v>
+        <v>50056.5</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22.33</v>
+        <v>22.42</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>905.08</v>
+        <v>1273.05</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1129,11 +1129,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>19.91</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>681.0700000000001</v>
+        <v>690.4400000000001</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37800.07</v>
+        <v>37790.7</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>30.02</v>
+        <v>70.62</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.77</v>
+        <v>64.28</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5408.73</v>
+        <v>5408.22</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.17</v>
@@ -1497,11 +1497,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1606,13 +1606,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1617.91</v>
+        <v>1628.19</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1914</v>
+        <v>1903.72</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>45.81</v>
+        <v>46.1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1621,11 +1621,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>55.76</v>
+        <v>199.46</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45763.68</v>
+        <v>50780.76</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>34153.89</v>
+        <v>29136.8</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>57.26</v>
+        <v>63.54</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>5017.09</v>
+        <v>5311.46</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4402.67</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>13052.32</v>
+        <v>13114.3</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7619.54</v>
+        <v>7557.56</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>63.14</v>
+        <v>63.44</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>449.87</v>
+        <v>833.21</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2204,13 +2204,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5760.83</v>
+        <v>5902.05</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2524.02</v>
+        <v>2382.8</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>69.53</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>188.5</v>
+        <v>247.48</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1446.2</v>
+        <v>1481.47</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5968.77</v>
+        <v>5933.5</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.5</v>
+        <v>19.98</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2405,11 +2405,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>141.09</v>
+        <v>180.01</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>756.26</v>
+        <v>1222.74</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2864,13 +2864,13 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>186.24</v>
+        <v>186.82</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2192.61</v>
+        <v>2192.03</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.83</v>
+        <v>7.85</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2879,11 +2879,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.58</v>
+        <v>3023.96</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
         <v>3431.79</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3430.45</v>
+        <v>3430.44</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.04</v>
@@ -3003,11 +3003,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3170,26 +3170,26 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>507.71</v>
+        <v>515.1900000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>64.61</v>
+        <v>57.13</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>88.70999999999999</v>
+        <v>90.02</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>8.779999999999999</v>
+        <v>49.53</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -3454,13 +3454,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7369.79</v>
+        <v>7887.38</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5876.43</v>
+        <v>5358.84</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>55.64</v>
+        <v>59.54</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3469,11 +3469,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>537.92</v>
+        <v>114.29</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3516,13 +3516,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>381.36</v>
+        <v>427.28</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9726.379999999999</v>
+        <v>9680.459999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.77</v>
+        <v>4.23</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3531,11 +3531,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>68.06</v>
+        <v>283.18</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6425.47</v>
+        <v>6542.91</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19045.57</v>
+        <v>18928.13</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>25.23</v>
+        <v>25.69</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3593,11 +3593,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>365.42</v>
+        <v>248.17</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3640,10 +3640,10 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3012.92</v>
+        <v>3014.32</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14246.62</v>
+        <v>14245.22</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>17.46</v>
@@ -3655,11 +3655,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>24.41</v>
+        <v>861.48</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>94.38</v>
+        <v>116.54</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3764,13 +3764,13 @@
         <v>10963.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>969.51</v>
+        <v>1169.77</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9993.82</v>
+        <v>9793.559999999999</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.84</v>
+        <v>10.67</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>200.26</v>
+        <v>37.99</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3826,13 +3826,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1874.55</v>
+        <v>1916.4</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7638.89</v>
+        <v>7597.04</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19.7</v>
+        <v>20.14</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3841,11 +3841,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>41.85</v>
+        <v>22.19</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>622.66</v>
+        <v>663.98</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4931.59</v>
+        <v>4890.27</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11.21</v>
+        <v>11.95</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4023,11 +4023,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>44.47</v>
+        <v>37.41</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4070,13 +4070,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>167.94</v>
+        <v>192.74</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>241.11</v>
+        <v>216.31</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41.06</v>
+        <v>47.12</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4085,11 +4085,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>24.84</v>
+        <v>0.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>44.66</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4594,13 +4594,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>38.1</v>
+        <v>38.18</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>233.28</v>
+        <v>233.2</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14.04</v>
+        <v>14.07</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4609,11 +4609,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4816,13 +4816,13 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>172.55</v>
+        <v>200.81</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>353.48</v>
+        <v>325.22</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>32.8</v>
+        <v>38.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4831,11 +4831,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>35.95</v>
+        <v>21.09</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4940,13 +4940,13 @@
         <v>243.93</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>69.52</v>
+        <v>84.16</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>174.41</v>
+        <v>159.77</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.5</v>
+        <v>34.5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4955,11 +4955,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>14.64</v>
+        <v>19.42</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5410,13 +5410,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>33128.47</v>
+        <v>33164.82</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34365.11</v>
+        <v>34328.76</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.08</v>
+        <v>49.14</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5425,11 +5425,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>61.32</v>
+        <v>47.12</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5472,13 +5472,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>24071.15</v>
+        <v>25974.28</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>39581.52</v>
+        <v>37678.39</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>37.82</v>
+        <v>40.81</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5487,11 +5487,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1912.82</v>
+        <v>9.69</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>31692.3</v>
+        <v>31887.04</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28460.61</v>
+        <v>28265.87</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>52.69</v>
+        <v>53.01</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5549,11 +5549,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>595.33</v>
+        <v>426.37</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5596,10 +5596,10 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>280.69</v>
+        <v>280.84</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19553.94</v>
+        <v>19553.79</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.42</v>
@@ -5611,11 +5611,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -6026,13 +6026,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>518.77</v>
+        <v>535.51</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>226.88</v>
+        <v>210.14</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>69.56999999999999</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6041,11 +6041,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>24.3</v>
+        <v>13.74</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         <v>3533.82</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>63.65</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3470.17</v>
+        <v>3469.14</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -6888,13 +6888,13 @@
         <v>15495.38</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4469.31</v>
+        <v>4470.09</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11026.08</v>
+        <v>11025.29</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.84</v>
+        <v>28.85</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6903,11 +6903,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7408,13 +7408,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>12498.36</v>
+        <v>13370.09</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13621.57</v>
+        <v>12749.84</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>47.85</v>
+        <v>51.19</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7423,11 +7423,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>871.73</v>
+        <v>23.76</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7470,13 +7470,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>29233.08</v>
+        <v>36459.31</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>88263.84</v>
+        <v>81037.61</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>24.88</v>
+        <v>31.03</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7485,11 +7485,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>8725.190000000001</v>
+        <v>1498.96</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7656,13 +7656,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>38482.62</v>
+        <v>38585.07</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19813.23</v>
+        <v>19710.78</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>66.01000000000001</v>
+        <v>66.19</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7671,11 +7671,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>384.04</v>
+        <v>5055.14</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7780,13 +7780,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5571.19</v>
+        <v>5886.34</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6028.89</v>
+        <v>5713.74</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48.03</v>
+        <v>50.74</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7795,11 +7795,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>502.72</v>
+        <v>426.76</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8192,13 +8192,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40581.11</v>
+        <v>40749.86</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>70117.75</v>
+        <v>69949</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>36.66</v>
+        <v>36.81</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8207,11 +8207,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>172.59</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8316,13 +8316,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1692.38</v>
+        <v>1941.98</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32609.95</v>
+        <v>32360.35</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.93</v>
+        <v>5.66</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8331,11 +8331,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>277.75</v>
+        <v>56.06</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8502,13 +8502,13 @@
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4256.51</v>
+        <v>4276.48</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15257.89</v>
+        <v>15237.92</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.81</v>
+        <v>21.91</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -8517,11 +8517,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>42.08</v>
+        <v>45.23</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>21-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -8626,13 +8626,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11562.28</v>
+        <v>11755.79</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11022.89</v>
+        <v>10829.38</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>51.19</v>
+        <v>52.05</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8641,11 +8641,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1436.14</v>
+        <v>1578.07</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8750,10 +8750,10 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>292.56</v>
+        <v>292.57</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.92</v>
+        <v>21.91</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>93.03</v>
@@ -8765,11 +8765,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>21.38</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9224,13 +9224,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2722.37</v>
+        <v>2887.49</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5272.77</v>
+        <v>5107.65</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>34.05</v>
+        <v>36.12</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9239,11 +9239,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>269.33</v>
+        <v>247.25</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9363,11 +9363,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>54.17</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9410,13 +9410,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>73.28</v>
+        <v>73.52</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1864.39</v>
+        <v>1864.15</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9425,11 +9425,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>35.45</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9636,13 +9636,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10229.27</v>
+        <v>10272.39</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28122.93</v>
+        <v>28079.81</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>26.67</v>
+        <v>26.78</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9651,11 +9651,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>43.12</v>
+        <v>263</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9698,13 +9698,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2269.14</v>
+        <v>2338.5</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12941.92</v>
+        <v>12872.56</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14.92</v>
+        <v>15.37</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9713,11 +9713,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>319.03</v>
+        <v>550.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9760,13 +9760,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3061.89</v>
+        <v>3154.94</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12556.13</v>
+        <v>12463.08</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9775,11 +9775,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>178.16</v>
+        <v>140.95</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -10128,13 +10128,13 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3101.42</v>
+        <v>3143.22</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2876.32</v>
+        <v>2834.52</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.88</v>
+        <v>52.58</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -10143,11 +10143,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>27-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1781.65</v>
+        <v>1761.32</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -618,13 +618,13 @@
         <v>137884.78</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>49.29</v>
+        <v>-97457.45</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>137835.49</v>
+        <v>235342.23</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.04</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>0.13</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -680,13 +680,13 @@
         <v>149318.61</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>149318.61</v>
+        <v>146327.6</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>2991.01</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -742,13 +742,13 @@
         <v>69730.64</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9661.85</v>
+        <v>-42047.03</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>60068.79</v>
+        <v>111777.67</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.86</v>
+        <v>-60.3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.39</v>
+        <v>4.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>120882.35</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4184.78</v>
+        <v>-24114.15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>116697.57</v>
+        <v>144996.5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.46</v>
+        <v>-19.95</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -819,11 +819,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>92.97</v>
+        <v>95.37</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         <v>115457.52</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>47809.29</v>
+        <v>37570.01</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>67648.23</v>
+        <v>77887.50999999999</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41.41</v>
+        <v>32.54</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         <v>103743.08</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>90082.78999999999</v>
+        <v>90059.78999999999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13660.29</v>
+        <v>13683.29</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>86.83</v>
+        <v>86.81</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -990,13 +990,13 @@
         <v>101232.21</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>27555.07</v>
+        <v>-6696.74</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>73677.14</v>
+        <v>107928.95</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>27.22</v>
+        <v>-6.62</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>24.12</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         <v>64523.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>14467.15</v>
+        <v>14187.8</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>50056.5</v>
+        <v>50335.85</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22.42</v>
+        <v>21.99</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1273.05</v>
+        <v>1241.62</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1176,13 +1176,13 @@
         <v>42512.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>193.25</v>
+        <v>-10718.26</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42319.5</v>
+        <v>53231.01</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.45</v>
+        <v>-25.21</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1191,11 +1191,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>19.91</v>
+        <v>16.87</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>38481.14</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>690.4400000000001</v>
+        <v>-31169.89</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>37790.7</v>
+        <v>69651.03</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.79</v>
+        <v>-81</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>70.62</v>
+        <v>33.49</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1362,13 +1362,13 @@
         <v>11830.05</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>11830.05</v>
+        <v>11805.55</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>100</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>9545.08</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
+        <v>-9293.5</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>9545.08</v>
+        <v>18838.58</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>-97.36</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1482,13 +1482,13 @@
         <v>5472.5</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.28</v>
+        <v>-5033.44</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5408.22</v>
+        <v>10505.94</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.17</v>
+        <v>-91.98</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1497,11 +1497,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.19</v>
+        <v>0.89</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1544,13 +1544,13 @@
         <v>2377.67</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7.71</v>
+        <v>-2314.84</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2369.96</v>
+        <v>4692.51</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.32</v>
+        <v>-97.36</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1559,11 +1559,11 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1606,13 +1606,13 @@
         <v>3531.91</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1628.19</v>
+        <v>1751.77</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1903.72</v>
+        <v>1780.14</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46.1</v>
+        <v>49.6</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1621,11 +1621,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>199.46</v>
+        <v>162</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1894,13 +1894,13 @@
         <v>79917.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>50780.76</v>
+        <v>55886.48</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29136.8</v>
+        <v>24031.08</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>63.54</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>5311.46</v>
+        <v>205.74</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         <v>53152.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>19357.93</v>
+        <v>19356.77</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33794.65</v>
+        <v>33795.81</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>36.42</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>4402.67</v>
+        <v>7522.97</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2080,13 +2080,13 @@
         <v>23294.11</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>12208.1</v>
+        <v>10761.79</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11086.01</v>
+        <v>12532.32</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>52.41</v>
+        <v>46.2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>20671.86</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>13114.3</v>
+        <v>13802.38</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7557.56</v>
+        <v>6869.48</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>63.44</v>
+        <v>66.77</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>833.21</v>
+        <v>347.98</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2204,13 +2204,13 @@
         <v>8284.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5902.05</v>
+        <v>5949.33</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2382.8</v>
+        <v>2335.52</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>71.23999999999999</v>
+        <v>71.81</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>247.48</v>
+        <v>348.13</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2266,13 +2266,13 @@
         <v>22682.31</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>11140.24</v>
+        <v>11319.82</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11542.07</v>
+        <v>11362.49</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>49.11</v>
+        <v>49.91</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>20-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2390,13 +2390,13 @@
         <v>7414.97</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1481.47</v>
+        <v>-4364.39</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5933.5</v>
+        <v>11779.36</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.98</v>
+        <v>-58.86</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2405,11 +2405,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>180.01</v>
+        <v>22.14</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2514,13 +2514,13 @@
         <v>5260.44</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1129.14</v>
+        <v>1033.67</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4131.3</v>
+        <v>4226.77</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21.46</v>
+        <v>19.65</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -2740,13 +2740,13 @@
         <v>8960.700000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10.69</v>
+        <v>-8941.469999999999</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8950.01</v>
+        <v>17902.17</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.12</v>
+        <v>-99.79000000000001</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2802,13 +2802,13 @@
         <v>6504.78</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1932.35</v>
+        <v>2688.82</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4572.43</v>
+        <v>3815.96</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29.71</v>
+        <v>41.34</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2817,11 +2817,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1222.74</v>
+        <v>466.26</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2864,13 +2864,13 @@
         <v>2378.85</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>186.82</v>
+        <v>-1874.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2192.03</v>
+        <v>4253.66</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.85</v>
+        <v>-78.81</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2879,11 +2879,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3023.96</v>
+        <v>3024.23</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2988,13 +2988,13 @@
         <v>3431.79</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.35</v>
+        <v>-3412.98</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3430.44</v>
+        <v>6844.77</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.04</v>
+        <v>-99.45</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3003,11 +3003,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         <v>3021.64</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>218.09</v>
+        <v>-108.29</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2803.55</v>
+        <v>3129.93</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.22</v>
+        <v>-3.58</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>413.05</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3112,13 +3112,13 @@
         <v>2806.15</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>-1368.45</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2806.15</v>
+        <v>4174.6</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>-48.77</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3170,13 +3170,13 @@
         <v>572.3200000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>515.1900000000001</v>
+        <v>557.3200000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>57.13</v>
+        <v>15</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>90.02</v>
+        <v>97.38</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3185,11 +3185,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>49.53</v>
+        <v>4.93</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3232,13 +3232,13 @@
         <v>427.29</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>33.12</v>
+        <v>-215.14</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>394.17</v>
+        <v>642.4299999999999</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.75</v>
+        <v>-50.35</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -3294,13 +3294,13 @@
         <v>13.35</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>-13.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13.35</v>
+        <v>26.69</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>-99.93000000000001</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3454,13 +3454,13 @@
         <v>13246.22</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7887.38</v>
+        <v>7869.65</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5358.84</v>
+        <v>5376.57</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>59.54</v>
+        <v>59.41</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3469,11 +3469,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>114.29</v>
+        <v>69.48</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3516,13 +3516,13 @@
         <v>10107.74</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>427.28</v>
+        <v>-5297.41</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9680.459999999999</v>
+        <v>15405.15</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.23</v>
+        <v>-52.41</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3531,11 +3531,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>283.18</v>
+        <v>271.52</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         <v>25471.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6542.91</v>
+        <v>5926.41</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18928.13</v>
+        <v>19544.63</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>25.69</v>
+        <v>23.27</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3593,11 +3593,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>248.17</v>
+        <v>0.21</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3640,13 +3640,13 @@
         <v>17259.54</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3014.32</v>
+        <v>1193.38</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14245.22</v>
+        <v>16066.16</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17.46</v>
+        <v>6.91</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3655,11 +3655,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>861.48</v>
+        <v>817.63</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3702,13 +3702,13 @@
         <v>13151.64</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>604.98</v>
+        <v>-4838.93</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12546.66</v>
+        <v>17990.57</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.6</v>
+        <v>-36.79</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3717,11 +3717,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>116.54</v>
+        <v>267.29</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -3764,13 +3764,13 @@
         <v>10963.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1169.77</v>
+        <v>-2577.89</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9793.559999999999</v>
+        <v>13541.22</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>10.67</v>
+        <v>-23.51</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>37.99</v>
+        <v>17.27</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3826,13 +3826,13 @@
         <v>9513.440000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1916.4</v>
+        <v>989.64</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7597.04</v>
+        <v>8523.799999999999</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20.14</v>
+        <v>10.4</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3841,11 +3841,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>22.19</v>
+        <v>80.44</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -3888,13 +3888,13 @@
         <v>9935.34</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>-9935.34</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>9935.34</v>
+        <v>19870.68</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3946,13 +3946,13 @@
         <v>8442.57</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8442.57</v>
+        <v>8437.15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>100</v>
+        <v>99.94</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         <v>5554.25</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>663.98</v>
+        <v>-2662.75</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4890.27</v>
+        <v>8217</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11.95</v>
+        <v>-47.94</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4023,11 +4023,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>37.41</v>
+        <v>55</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4070,13 +4070,13 @@
         <v>409.05</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>192.74</v>
+        <v>193.14</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>216.31</v>
+        <v>215.91</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>47.12</v>
+        <v>47.22</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4085,11 +4085,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.4</v>
+        <v>20.84</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -4132,13 +4132,13 @@
         <v>31.27</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.55</v>
+        <v>-25.79</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.72</v>
+        <v>57.06</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.77</v>
+        <v>-82.48999999999999</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -4296,13 +4296,13 @@
         <v>928.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>116.09</v>
+        <v>-479.95</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>812.4</v>
+        <v>1408.44</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12.5</v>
+        <v>-51.69</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>13.08</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4358,13 +4358,13 @@
         <v>1497.03</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>276.48</v>
+        <v>279.53</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1220.55</v>
+        <v>1217.5</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18.47</v>
+        <v>18.67</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4373,11 +4373,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>86.11</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4420,13 +4420,13 @@
         <v>515.2</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>-351.34</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>515.2</v>
+        <v>866.54</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>-68.2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4478,13 +4478,13 @@
         <v>494.45</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>-107.62</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>494.45</v>
+        <v>602.0700000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>-21.77</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         <v>278.54</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>-278.54</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>278.54</v>
+        <v>557.08</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4594,13 +4594,13 @@
         <v>271.38</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>38.18</v>
+        <v>-40.5</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>233.2</v>
+        <v>311.88</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14.07</v>
+        <v>-14.92</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4609,11 +4609,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -4656,13 +4656,13 @@
         <v>271.23</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>-229.65</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>271.23</v>
+        <v>500.88</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>-84.67</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4816,13 +4816,13 @@
         <v>526.03</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>200.81</v>
+        <v>208.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>325.22</v>
+        <v>317.53</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>38.17</v>
+        <v>39.64</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4831,11 +4831,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>21.09</v>
+        <v>13.39</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4940,13 +4940,13 @@
         <v>243.93</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>84.16</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>159.77</v>
+        <v>166.17</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>34.5</v>
+        <v>31.88</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5002,13 +5002,13 @@
         <v>35.59</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1</v>
+        <v>-5.34</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>35.49</v>
+        <v>40.93</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.28</v>
+        <v>-15</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5122,13 +5122,13 @@
         <v>44.89</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>12.56</v>
+        <v>-4.83</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>32.33</v>
+        <v>49.72</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>27.98</v>
+        <v>-10.76</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -5184,13 +5184,13 @@
         <v>60.94</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4.11</v>
+        <v>-39.3</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>56.83</v>
+        <v>100.24</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6.74</v>
+        <v>-64.48999999999999</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5348,13 +5348,13 @@
         <v>33586.54</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4.14</v>
+        <v>-23086.68</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33582.4</v>
+        <v>56673.22</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.01</v>
+        <v>-68.73999999999999</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -5410,13 +5410,13 @@
         <v>67493.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>33164.82</v>
+        <v>19865.28</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34328.76</v>
+        <v>47628.3</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.14</v>
+        <v>29.43</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -5425,11 +5425,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>47.12</v>
+        <v>82.89</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5472,13 +5472,13 @@
         <v>63652.67</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>25974.28</v>
+        <v>21780.25</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>37678.39</v>
+        <v>41872.42</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>40.81</v>
+        <v>34.22</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5487,11 +5487,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>9.69</v>
+        <v>18.44</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>60152.91</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>31887.04</v>
+        <v>30286.31</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28265.87</v>
+        <v>29866.6</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>53.01</v>
+        <v>50.35</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -5549,11 +5549,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>426.37</v>
+        <v>68.84</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5596,13 +5596,13 @@
         <v>19834.63</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>280.84</v>
+        <v>-18985.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19553.79</v>
+        <v>38819.77</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.42</v>
+        <v>-95.72</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -5658,13 +5658,13 @@
         <v>29457.81</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>24.31</v>
+        <v>-28371.1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29433.5</v>
+        <v>57828.91</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.08</v>
+        <v>-96.31</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -5673,11 +5673,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>10.41</v>
+        <v>1.96</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5720,13 +5720,13 @@
         <v>26549.48</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1541.23</v>
+        <v>1567.08</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25008.24</v>
+        <v>24982.4</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5.81</v>
+        <v>5.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -5735,11 +5735,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>25.83</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -5782,13 +5782,13 @@
         <v>33670.61</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>-32015.75</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>33670.61</v>
+        <v>65686.36</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>-95.09</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -5902,13 +5902,13 @@
         <v>21283.6</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>21283.6</v>
+        <v>21208.31</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>100</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -6026,13 +6026,13 @@
         <v>745.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>535.51</v>
+        <v>536.01</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>210.14</v>
+        <v>209.64</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>71.81999999999999</v>
+        <v>71.89</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -6041,11 +6041,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>13.74</v>
+        <v>12.09</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>11.95</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -6252,13 +6252,13 @@
         <v>77.95</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>-77.95</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>77.95</v>
+        <v>155.9</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -6310,13 +6310,13 @@
         <v>19.56</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>-19.56</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>19.56</v>
+        <v>39.12</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -6426,13 +6426,13 @@
         <v>8.69</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>-8.69</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8.69</v>
+        <v>17.38</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -6484,13 +6484,13 @@
         <v>29.05</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>-29.05</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29.05</v>
+        <v>58.1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -6542,13 +6542,13 @@
         <v>7.27</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4.59</v>
+        <v>-2.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2.68</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>63.14</v>
+        <v>-36.86</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -6604,13 +6604,13 @@
         <v>5.43</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>-5.43</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5.43</v>
+        <v>10.86</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -6826,13 +6826,13 @@
         <v>5166.66</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>711.2</v>
+        <v>487.9</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4455.47</v>
+        <v>4678.76</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.77</v>
+        <v>9.44</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -6888,13 +6888,13 @@
         <v>15495.38</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4470.09</v>
+        <v>-1046.22</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11025.29</v>
+        <v>16541.6</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.85</v>
+        <v>-6.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6950,13 +6950,13 @@
         <v>6925.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>-6925.39</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6925.39</v>
+        <v>13850.78</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -7008,13 +7008,13 @@
         <v>4217.06</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>-4217.06</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4217.06</v>
+        <v>8434.120000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -7066,13 +7066,13 @@
         <v>1478.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2.18</v>
+        <v>-1457.47</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1476.57</v>
+        <v>2936.22</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.15</v>
+        <v>-98.56</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7128,13 +7128,13 @@
         <v>4094.55</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>-4076.93</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4094.55</v>
+        <v>8171.48</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>-99.56999999999999</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -7186,13 +7186,13 @@
         <v>554.14</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>-475.84</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>554.14</v>
+        <v>1029.98</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>-85.87</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7408,13 +7408,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>13370.09</v>
+        <v>11864.99</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12749.84</v>
+        <v>14254.94</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>51.19</v>
+        <v>45.43</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>23.76</v>
+        <v>28.58</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7470,13 +7470,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>36459.31</v>
+        <v>28726.53</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>81037.61</v>
+        <v>88770.39</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>31.03</v>
+        <v>24.45</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7485,11 +7485,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1498.96</v>
+        <v>5.94</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7532,22 +7532,22 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>33783.39</v>
+        <v>33697.42</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>85.97</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>100</v>
+        <v>99.75</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -7656,13 +7656,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>38585.07</v>
+        <v>41134.81</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19710.78</v>
+        <v>17161.04</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>66.19</v>
+        <v>70.56</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7671,11 +7671,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5055.14</v>
+        <v>872.92</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7718,13 +7718,13 @@
         <v>38881.49</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>35814.93</v>
+        <v>35806.5</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3066.56</v>
+        <v>3074.99</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>92.11</v>
+        <v>92.09</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -7780,13 +7780,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5886.34</v>
+        <v>6120.55</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5713.74</v>
+        <v>5479.53</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>50.74</v>
+        <v>52.76</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -7795,11 +7795,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>426.76</v>
+        <v>543.12</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7842,13 +7842,13 @@
         <v>2874.21</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2874.21</v>
+        <v>2873.59</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>100</v>
+        <v>99.98</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -7904,22 +7904,22 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2943.83</v>
+        <v>2926.03</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -8192,13 +8192,13 @@
         <v>110698.86</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40749.86</v>
+        <v>40437.51</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>69949</v>
+        <v>70261.35000000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>36.81</v>
+        <v>36.53</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8207,11 +8207,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>17.53</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8316,13 +8316,13 @@
         <v>34302.33</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1941.98</v>
+        <v>-26172.05</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>32360.35</v>
+        <v>60474.38</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.66</v>
+        <v>-76.3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8331,11 +8331,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>56.06</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8378,17 +8378,17 @@
         <v>26019.96</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>26019.96</v>
+        <v>25372.22</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>647.74</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>100</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -8440,13 +8440,13 @@
         <v>25510.91</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>20736.41</v>
+        <v>8002.32</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4774.5</v>
+        <v>17508.59</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>81.28</v>
+        <v>31.37</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8502,13 +8502,13 @@
         <v>19514.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4276.48</v>
+        <v>4321.71</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15237.92</v>
+        <v>15192.69</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.91</v>
+        <v>22.15</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -8517,11 +8517,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>45.23</v>
+        <v>0.87</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8626,13 +8626,13 @@
         <v>22585.17</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11755.79</v>
+        <v>13310.48</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10829.38</v>
+        <v>9274.690000000001</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>52.05</v>
+        <v>58.93</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8641,11 +8641,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1578.07</v>
+        <v>141.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -8688,13 +8688,13 @@
         <v>1878.7</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46.9</v>
+        <v>-444.95</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1831.8</v>
+        <v>2323.65</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.5</v>
+        <v>-23.68</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -8703,11 +8703,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -8750,13 +8750,13 @@
         <v>314.48</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>292.57</v>
+        <v>292.61</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.91</v>
+        <v>21.87</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>93.03</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8765,11 +8765,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -8914,13 +8914,13 @@
         <v>54334.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>54334.43</v>
+        <v>54008.97</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>325.46</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>21.38</v>
+        <v>48.84</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9224,13 +9224,13 @@
         <v>7995.14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2887.49</v>
+        <v>3126.04</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5107.65</v>
+        <v>4869.1</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36.12</v>
+        <v>39.1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -9239,11 +9239,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>247.25</v>
+        <v>137.42</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9348,13 +9348,13 @@
         <v>6968.09</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6968.09</v>
+        <v>6857.52</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>110.57</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>98.41</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -9410,13 +9410,13 @@
         <v>1937.67</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>73.52</v>
+        <v>-1072.35</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1864.15</v>
+        <v>3010.02</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.79</v>
+        <v>-55.34</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -9425,11 +9425,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9472,13 +9472,13 @@
         <v>1831.54</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1795.47</v>
+        <v>1830.92</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>36.07</v>
+        <v>0.62</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>98.03</v>
+        <v>99.97</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -9487,11 +9487,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>35.45</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -9636,13 +9636,13 @@
         <v>38352.2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10272.39</v>
+        <v>-4175.65</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28079.81</v>
+        <v>42527.85</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>26.78</v>
+        <v>-10.89</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>263</v>
+        <v>1029.03</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -9698,13 +9698,13 @@
         <v>15211.06</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2338.5</v>
+        <v>123.82</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12872.56</v>
+        <v>15087.24</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15.37</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -9713,11 +9713,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>550.5</v>
+        <v>204.91</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9760,13 +9760,13 @@
         <v>15618.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3154.94</v>
+        <v>1466.02</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>12463.08</v>
+        <v>14152</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20.2</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -9775,11 +9775,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>140.95</v>
+        <v>101.29</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9884,13 +9884,13 @@
         <v>13880.42</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1961.14</v>
+        <v>-3146.73</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11919.27</v>
+        <v>17027.15</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14.13</v>
+        <v>-22.67</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -9946,13 +9946,13 @@
         <v>11752.33</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5415.79</v>
+        <v>824.96</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6336.54</v>
+        <v>10927.37</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46.08</v>
+        <v>7.02</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -10008,13 +10008,13 @@
         <v>11254.86</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0</v>
+        <v>-3610.46</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11254.86</v>
+        <v>14865.32</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>-32.08</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -10128,13 +10128,13 @@
         <v>5977.74</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3143.22</v>
+        <v>4370.65</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2834.52</v>
+        <v>1607.09</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>52.58</v>
+        <v>73.12</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -10143,11 +10143,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-10-2026</t>
+          <t>28-10-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1761.32</v>
+        <v>21.63</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -10190,13 +10190,13 @@
         <v>2917.88</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>18.72</v>
+        <v>-19.92</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2899.16</v>
+        <v>2937.8</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.64</v>
+        <v>-0.68</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -10252,13 +10252,13 @@
         <v>20.53</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>-20.53</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.53</v>
+        <v>41.06</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-flat-dashboard.xlsx
+++ b/public/data/eu-steel-trq-flat-dashboard.xlsx
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>95.37</v>
+        <v>134.14</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1241.62</v>
+        <v>2374.95</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>16.87</v>
+        <v>36.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>33.49</v>
+        <v>41.04</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>162</v>
+        <v>313.53</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>347.98</v>
+        <v>611.59</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>348.13</v>
+        <v>476.61</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>22.14</v>
+        <v>29.75</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>125.39</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>466.26</v>
+        <v>680.33</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4.93</v>
+        <v>6.76</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>69.48</v>
+        <v>138.27</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>271.52</v>
+        <v>279.46</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.21</v>
+        <v>38.12</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>817.63</v>
+        <v>1395.22</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>80.44</v>
+        <v>428.04</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>55</v>
+        <v>62.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>20.84</v>
+        <v>24.28</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18.44</v>
+        <v>525.95</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>68.84</v>
+        <v>1132.64</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>56.99</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>12.09</v>
+        <v>28.26</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>28.58</v>
+        <v>30.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>872.92</v>
+        <v>899.76</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>543.12</v>
+        <v>899.95</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>29.01</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>17.53</v>
+        <v>1396.06</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>85.23999999999999</v>
+        <v>173.45</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>141.7</v>
+        <v>388.98</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>137.42</v>
+        <v>356.58</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.89</v>
+        <v>2.22</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>204.91</v>
+        <v>389.55</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>101.29</v>
+        <v>168.55</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
